--- a/LeetCode.xlsx
+++ b/LeetCode.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\pyworkspace\Leetcode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenchen/Projects/Leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570FD1C1-341D-494B-9484-F209371E515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DEC19C-C1B3-6E4D-A7D6-27516BC12DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28340" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LeetCode" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId2"/>
-    <sheet name="LC-SQL" sheetId="8" r:id="rId3"/>
-    <sheet name="GS" sheetId="1" r:id="rId4"/>
-    <sheet name="2S" sheetId="7" r:id="rId5"/>
-    <sheet name="progress" sheetId="4" r:id="rId6"/>
-    <sheet name="topics" sheetId="6" r:id="rId7"/>
-    <sheet name="playground" sheetId="9" r:id="rId8"/>
+    <sheet name="LC-SQL" sheetId="8" r:id="rId2"/>
+    <sheet name="GS" sheetId="1" r:id="rId3"/>
+    <sheet name="2S" sheetId="7" r:id="rId4"/>
+    <sheet name="progress" sheetId="4" r:id="rId5"/>
+    <sheet name="topics" sheetId="6" r:id="rId6"/>
+    <sheet name="playground" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'LC-SQL'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LeetCode!$A$1:$L$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LC-SQL'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LeetCode!$A$1:$M$157</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="528">
   <si>
     <t>#</t>
   </si>
@@ -479,1438 +478,1427 @@
   <si>
     <t>不停给set (hash table)加，看set长度有没有变</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Min Stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要getMin也要O(1)，就不可以用heap，binary search tree。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用另外一个stack记录到这一层为止的min_val。只要最上面的值不变，下面每一层的min_val都是不变的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decode String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Calculator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack记录括号外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack记录括号外，很多特殊情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Calculator II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全用stack。每个符号都先pop，计算，再push</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daily Temperatures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trapping Rain Water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存多少水取决于左边的max，右边的max。从左扫一遍cummax，left_max；从右扫一遍cummax，right_max。水量就是min(left_max[i,] righ_max[i])-val[i]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove All Adjacent Duplicates in String II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Moving Average from Data Stream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implement Queue using Stacks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pop Time complexity: Amortized O(1), Worst-case O(n).
+两个stack，一个正常push，需要pop的话，就把stack1倒到stack2，然后stack2去pop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validate Binary Search Tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree, dfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recursive看每个node是不是binary tree。把每个recurve的结果保存最大，最小值，上浮和node比较</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree, bfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Top K Frequent Elements</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用Counter，再heapq.nlargest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python用Counter里的most_common</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove Nth Node From End of List</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list, two pointers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遍历一遍计list长度，再遍历一遍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次用stack，再pop N个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个指针，第一个永远比第二个多N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delete Node in a Linked List</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单向链表，不知道前一个node，所以只能把下一个node值填过来，然后把下一个node删掉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heap, sliding window, deque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用heap，那么heap[0]就是最大值，但是heap插入是nlog(n)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dp[i]=min(dp[i-coin1], dp[i-coin2], …)+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://blog.csdn.net/sinat_15723179/article/details/82183985</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merge Two Binary Trees</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>recursive, dfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest Common Prefix    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Serialize and Deserialize Binary Tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有限制顺序，所以可以bfs也可以dfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search a 2D Matrix II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divide and conquer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左下角扫到右上角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lowest Common Ancestor of a Binary Tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfs遍历树，记录p,q两点的路径。再抽取相同路径。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K Closest Points to Origin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heap, sort, divide and conquer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack用来bfs遍历树，dict用来存node-parent(node)的关系。然后找出p的所有parent放在set里。然后找q的parent直到也出现在p的parent里。这时候的q就是。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>heap.nsmallest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divide and conquer，快排的partition方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minimum Remove to Make Valid Parentheses</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack放括号，剩下的是需要删除的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>two pointers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sliding window</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>binary search tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Copy List with Random Pointer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当做图一个个节点，然后遍历。遍历过的新节点就放起来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search a 2D Matrix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delete Node in a BST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reverse Words in a String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>database</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combine Two Tables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>left join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>two pointers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3Sum With Multiplicity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Counter，然后分情况计数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find Smallest Common Element in All Rows</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash table, binary search</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个row都放在set里，intersection取最小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advantage Shuffle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array, greedy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pacific Atlantic Water Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfs, bfs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>medium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add Two Numbers II</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deque实现bfs，从边缘点bfs比边缘点大的。分pacific, atlantic找，最后intersection就是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merge k Sorted Lists</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两两比较，比较k-1次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Subtree of Another Tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看当前是不是isMatch(),递归s的左右节点看是不是isSubtree()。isMatch()也递归的比较</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list, heap, divide and conquer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove Linked List Elements</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意连续满足条件的情况，只有不删除时候才curr=curr.next</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intersection of Two Linked Lists</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list, hash table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先把list上每个node复制，跟在后面，再复制random指针，再拆分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不给head，给被删的node</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先reverse再，像第二题一样add，再reverse。reverse list的写法熟练。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>green frequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow frequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blue frequent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack, two pointers, dp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack里还要能O(1)取到最小值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用stack实现queue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连续凑够k个字母就删掉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack每个元素存（字母，累积数目）的配对</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先遍历一遍知道长度，再stack做法。空间O(n)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先翻转左边链表，再两个指针不停next对比。空间O(1)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>review</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某个点开始两个list汇成一个list，找到那个点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看list有没有cycle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复制list，且有random指针</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去掉倒数第N个节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个list表示两个数从个位开始，相加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去掉所有特定值的节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list翻转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1,n]范围内取n+1个数字，找重复的那个数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sorted array里找数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从左上角到右下单调增，每行第一个比上一行最后一个大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>把整个矩阵当做一个单调序列，还是普通binary search。只是中点元素是哪个需要算一下对应到矩阵里。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每行都单调增，找各行交集的最小值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不重复的最长子序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stack里记录的值肯定是单调减的。stack记录loc和value。有new high就把stack pop一遍，直到没有new high。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看简便做法板子，四步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有和是target的三个数的总数，多次出现算多次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个矩阵从左往右递增，从上往下递增；给定个数，判断这个数出不出现。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>binary search</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove Element</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array, two pointers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不使用额外空间删除list里元素。顺序无所谓。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双指针，一个拖后写有效值，一个判断是不是val。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>K-th Element of Two Sorted Arrays</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/k-th-element-two-sorted-arrays/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brick Wall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多少墙板穿不过去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最少能凑够数额的硬币数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maximum Subarray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Design HashMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>easy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>linked list, array, hash table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整数key实现hashmap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash function用modulo，collision用array。平均O(1)，最差O(n)。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法导论第11章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这题用direct address table也可以。就是memory占用更多。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power of Two</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>math</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Longest Common Subsequence</t>
+  </si>
+  <si>
+    <t>dp</t>
+  </si>
+  <si>
+    <t>两个字符串找最长公共子序列</t>
+  </si>
+  <si>
+    <t>初始化dp时候注意不要浅拷贝</t>
+  </si>
+  <si>
+    <t>Contains Duplicate</t>
+  </si>
+  <si>
+    <t>n &amp; (n-1) == 0</t>
+  </si>
+  <si>
+    <t>看一个数是否是2的次方</t>
+  </si>
+  <si>
+    <t>hash table</t>
+  </si>
+  <si>
+    <t>是否存在重复数</t>
+  </si>
+  <si>
+    <t>寻找sum最大连续子序列</t>
+  </si>
+  <si>
+    <t>Divide Two Integers</t>
+  </si>
+  <si>
+    <t>Multiply Strings</t>
+  </si>
+  <si>
+    <t>Add Strings</t>
+  </si>
+  <si>
+    <t>Find Nearest Point That Has the Same X or Y Coordinate</t>
+  </si>
+  <si>
+    <t>Median of Two Sorted Arrays</t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>Maximum Subarray</t>
+  </si>
+  <si>
+    <t>LRU</t>
+  </si>
+  <si>
+    <t>Find the Closest Palindrome</t>
+  </si>
+  <si>
+    <t>Design Circular Queue</t>
+  </si>
+  <si>
+    <t>array, queue</t>
+  </si>
+  <si>
+    <t>self.headIndex + self.count) % self.capacity用来描述新的head对应的queue的位置。随着head一栋，所有位置都用相对head的位置来描述。</t>
+  </si>
+  <si>
+    <t>Walls and Gates</t>
+  </si>
+  <si>
+    <t>bfs</t>
+  </si>
+  <si>
+    <t>matrix里填空白地方到最近gate的距离</t>
+  </si>
+  <si>
+    <t>Number of Islands</t>
+  </si>
+  <si>
+    <t>bfs, dfs</t>
+  </si>
+  <si>
+    <t>matrix有陆地有水，数有多少块陆地被水隔开</t>
+  </si>
+  <si>
+    <t>Sort the Matrix Diagonally</t>
+  </si>
+  <si>
+    <t>Squarepoint</t>
+  </si>
+  <si>
+    <t>每条对角线排序。字典存diagonal更快，key是row-col，value是一个list</t>
+  </si>
+  <si>
+    <t>Longest Increasing Subsequence</t>
+  </si>
+  <si>
+    <t>binary search, dp</t>
+  </si>
+  <si>
+    <t>solution里有dp教学</t>
+  </si>
+  <si>
+    <t>dp得到答案o(n^2)，更新每个dp时候需要和所有之前的dp比</t>
+  </si>
+  <si>
+    <t>Check if Every Row and Column Contains All Numbers</t>
+  </si>
+  <si>
+    <t>hash table存每行每列出现个数，最后看个数是不是1</t>
+  </si>
+  <si>
+    <t>Matrix Diagonal Sum</t>
+  </si>
+  <si>
+    <t>Valid Sudoku</t>
+  </si>
+  <si>
+    <t>同2133，hash table存每行每列每块出现个数，最后看个数是不是&lt;=1</t>
+  </si>
+  <si>
+    <t>Perfect Squares</t>
+  </si>
+  <si>
+    <t>给定的数，最少需要多少个完全平方数可以加和组成</t>
+  </si>
+  <si>
+    <t>dp, bfs</t>
+  </si>
+  <si>
+    <t>dp[i]=min(dp[i],dp[i-square]+1)。遍历square nums，而不是所有组合，减少复杂度</t>
+  </si>
+  <si>
+    <t>Flood Fill</t>
+  </si>
+  <si>
+    <t>dfs, bfs</t>
+  </si>
+  <si>
+    <t>Keys and Rooms</t>
+  </si>
+  <si>
+    <t>01 Matrix</t>
+  </si>
+  <si>
+    <t>Implement Stack using Queues</t>
+  </si>
+  <si>
+    <t>queue</t>
+  </si>
+  <si>
+    <t>一个queue。push时候新的放在前面，旧的全部push一遍。</t>
+  </si>
+  <si>
+    <t>Open the Lock</t>
+  </si>
+  <si>
+    <t>bfs, hash table</t>
+  </si>
+  <si>
+    <t>转密码锁但不能碰到一些数字，找shortest path</t>
+  </si>
+  <si>
+    <t>每个组合当做graph上面的一个node，可以转一次得到的node之间有edge。然后是bfs找shortest path</t>
+  </si>
+  <si>
+    <t>Single Number</t>
+  </si>
+  <si>
+    <t>Happy Number</t>
+  </si>
+  <si>
+    <t>hash table, two pointers</t>
+  </si>
+  <si>
+    <t>看是happy number还是无限循环</t>
+  </si>
+  <si>
+    <t>Design Linked List</t>
+  </si>
+  <si>
+    <t>linked list</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
+  </si>
+  <si>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>Clone Graph</t>
+  </si>
+  <si>
+    <t>bfs, dfs, hash table</t>
+  </si>
+  <si>
+    <t>Target Sum</t>
+  </si>
+  <si>
+    <t>[0,0,0,0,0,0,0,0,1]\n 1\n</t>
+  </si>
+  <si>
+    <t>recursion，但hash table记录visited避免重复计算</t>
+  </si>
+  <si>
+    <t>dp, hash table, backtracking</t>
+  </si>
+  <si>
+    <t>Binary Tree Inorder Traversal</t>
+  </si>
+  <si>
+    <t>dfs, stack, binary tree</t>
+  </si>
+  <si>
+    <t>中序遍历，left-mid-right</t>
+  </si>
+  <si>
+    <t>每个新node，split成[left, node, right]。stack里再多记录node是否split过。split过可以加到result，否则继续留着等split。</t>
+  </si>
+  <si>
+    <t>所有gate同时开始bfs填距离，先填距离的一定是最短的距离。天然不用存visited情况，因为empty相当于记录了。看距离，所以也只能用bfs不能用dfs。</t>
+  </si>
+  <si>
+    <t>陆地到海边的距离</t>
+  </si>
+  <si>
+    <t>每次海向内陆淹一公里，并填新的距离。用queue填海边borders，bfs。</t>
+  </si>
+  <si>
+    <t>Floyd's Tortoise and Hare，相当于找cycle起点问题
+https://blog.csdn.net/u013832707/article/details/103469112</t>
+  </si>
+  <si>
+    <t>Linked List Cycle II</t>
+  </si>
+  <si>
+    <t>linked list, hash table, two pointers</t>
+  </si>
+  <si>
+    <t>先A链存set，再B链看是否in set</t>
+  </si>
+  <si>
+    <t>cycle找起点</t>
+  </si>
+  <si>
+    <t>Odd Even Linked List</t>
+  </si>
+  <si>
+    <t>linked list, two pointers</t>
+  </si>
+  <si>
+    <t>奇数全放左边，偶数全放右边</t>
+  </si>
+  <si>
+    <t>two pointer，slow记录最后一个奇数，fast遍历list</t>
+  </si>
+  <si>
+    <t>linked list, stack</t>
+  </si>
+  <si>
+    <t>Rotate List</t>
+  </si>
+  <si>
+    <t>list保持顺序进行rotate</t>
+  </si>
+  <si>
+    <t>先生成cycle，再cut</t>
+  </si>
+  <si>
+    <t>Insert into a Sorted Circular Linked List</t>
+  </si>
+  <si>
+    <t>Flatten a Multilevel Doubly Linked List</t>
+  </si>
+  <si>
+    <t>linked list, dfs</t>
+  </si>
+  <si>
+    <t>带child指针的多层linked list flatten</t>
+  </si>
+  <si>
+    <t>用stack</t>
+  </si>
+  <si>
+    <t>Divide a String Into Groups of Size k</t>
+  </si>
+  <si>
+    <t>Minimum Moves to Reach Target Score</t>
+  </si>
+  <si>
+    <t>Solving Questions With Brainpower</t>
+  </si>
+  <si>
+    <t>Maximum Running Time of N Computers</t>
+  </si>
+  <si>
+    <t>Maximize Distance to Closest Person</t>
+  </si>
+  <si>
+    <t>找座位尽量和别人离的远</t>
+  </si>
+  <si>
+    <t>Game Play Analysis I</t>
+  </si>
+  <si>
+    <t>每个player第一次登陆日期</t>
+  </si>
+  <si>
+    <t>group by player_id后去登陆日期min</t>
+  </si>
+  <si>
+    <t>Game Play Analysis II</t>
+  </si>
+  <si>
+    <t>每个player第一次登陆日期对应的device</t>
+  </si>
+  <si>
+    <t>where的pair用法</t>
+  </si>
+  <si>
+    <t>Word Pattern</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-running-time-of-n-computers/discuss/1692939/JavaC%2B%2BPython-Sort-Solution-with-Explanation-O(mlogm)</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/maximum-running-time-of-n-computers/solution/liang-chong-jie-fa-er-fen-da-an-pai-xu-t-grd8/</t>
+  </si>
+  <si>
+    <t>upper bound=sum(A)//n。超过平均值的，那些电池给一个电脑从头用到尾，所以不考虑这个电脑也不考虑这个电池。
+当最大的都不够平均值，那么答案就是剩下的所有电池混用能够维持的最大时间。</t>
+  </si>
+  <si>
+    <t>Can Place Flowers</t>
+  </si>
+  <si>
+    <t>Isomorphic Strings</t>
+  </si>
+  <si>
+    <t>Minimum Index Sum of Two Lists</t>
+  </si>
+  <si>
+    <t>First Unique Character in a String</t>
+  </si>
+  <si>
+    <t>Contains Duplicate II</t>
+  </si>
+  <si>
+    <t>Logger Rate Limiter</t>
+  </si>
+  <si>
+    <t>Group Anagrams</t>
+  </si>
+  <si>
+    <t>key存字符串排序</t>
+  </si>
+  <si>
+    <t>Anagrams字母只有顺序不同</t>
+  </si>
+  <si>
+    <t>Group Shifted Strings</t>
+  </si>
+  <si>
+    <t>字符串平移的合并为一组</t>
+  </si>
+  <si>
+    <t>用ord字符串diff的和拼成key。字符串zfill，自动补零。</t>
+  </si>
+  <si>
+    <t>Find Duplicate Subtrees</t>
+  </si>
+  <si>
+    <t>遍历tree，subtree序列化成字符串存到dict里</t>
+  </si>
+  <si>
+    <t>hash table, sliding window, two pointers</t>
+  </si>
+  <si>
+    <t>two pointers做</t>
+  </si>
+  <si>
+    <t>4Sum II</t>
+  </si>
+  <si>
+    <t>四个都加是n^4。先加前两个，再加后两个。再two sum。那就是n^2。</t>
+  </si>
+  <si>
+    <t>四个数的sum为target</t>
+  </si>
+  <si>
+    <t>Unique Word Abbreviation</t>
+  </si>
+  <si>
+    <t>Insert Delete GetRandom O(1)</t>
+  </si>
+  <si>
+    <t>hash table, design</t>
+  </si>
+  <si>
+    <t>同时时间insert, delete, getrandom的O(1)操作</t>
+  </si>
+  <si>
+    <t>元素存list里，dict里存val:index，这样可以delete常数。</t>
+  </si>
+  <si>
+    <t>Guess Number Higher or Lower</t>
+  </si>
+  <si>
+    <t>binary search</t>
+  </si>
+  <si>
+    <t>api版的猜数</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>list增序，但旋转几位</t>
+  </si>
+  <si>
+    <t>先binary search出start_index，再search出value</t>
+  </si>
+  <si>
+    <t>House Robber</t>
+  </si>
+  <si>
+    <t>强盗按顺序抢房子里钱，不能抢相邻的。</t>
+  </si>
+  <si>
+    <t>Min Cost Climbing Stairs</t>
+  </si>
+  <si>
+    <t>backtracking，bp</t>
+  </si>
+  <si>
+    <t>back，bp</t>
+  </si>
+  <si>
+    <t>从后向前，bp</t>
+  </si>
+  <si>
+    <t>按顺序做题，可以选择跳题，每解一题，就必须要有一些题跳过</t>
+  </si>
+  <si>
+    <t>N-th Tribonacci Number</t>
+  </si>
+  <si>
+    <t>三数相加fibonacci</t>
+  </si>
+  <si>
+    <t>Delete and Earn</t>
+  </si>
+  <si>
+    <t>同198类似</t>
+  </si>
+  <si>
+    <t>一个数选了，那前后1格数字都不能选</t>
+  </si>
+  <si>
+    <t>Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t>Maximum Score from Performing Multiplication Operations</t>
+  </si>
+  <si>
+    <t>Maximal Square</t>
+  </si>
+  <si>
+    <t>找最大的全是1的方块，求面积</t>
+  </si>
+  <si>
+    <t>dp[i,j]=[i,j]作为终点的最大的全是1方块</t>
+  </si>
+  <si>
+    <t>DP[i][j] represents the longest common subsequence of text1[0 ... i] &amp; text2[0 ... j].dp[i][j] = dp[i – 1][j – 1] + 1 if text1[i – 1] == text2[j – 1] else max(dp[i][j – 1], dp[i – 1][j])</t>
+  </si>
+  <si>
+    <t>Find if Path Exists in Graph</t>
+  </si>
+  <si>
+    <t>看图上两点是否相连</t>
+  </si>
+  <si>
+    <t>stack每格存(path, visited)</t>
+  </si>
+  <si>
+    <t>stack每格存(curr_node)，有公共的visited set</t>
+  </si>
+  <si>
+    <t>All Paths From Source to Target</t>
+  </si>
+  <si>
+    <t>找图上两点间所有path</t>
+  </si>
+  <si>
+    <t>复制一个graph</t>
+  </si>
+  <si>
+    <t>有个dict存旧node和新node的关系，再dfs</t>
+  </si>
+  <si>
+    <t>Reconstruct Itinerary</t>
+  </si>
+  <si>
+    <t>Number of Connected Components in an Undirected Graph</t>
+  </si>
+  <si>
+    <t>有多少个连接块</t>
+  </si>
+  <si>
+    <t>Number of Provinces</t>
+  </si>
+  <si>
+    <t>同323</t>
+  </si>
+  <si>
+    <t>Count Elements With Strictly Smaller and Greater Elements</t>
+  </si>
+  <si>
+    <t>Rearrange Array Elements by Sign</t>
+  </si>
+  <si>
+    <t>Find All Lonely Numbers in the Array</t>
+  </si>
+  <si>
+    <t>Maximum Good People Based on Statements</t>
+  </si>
+  <si>
+    <t>dfs遍历所有可能，暴力检查</t>
+  </si>
+  <si>
+    <t>n个人互相说真假，最多多少人说真话</t>
+  </si>
+  <si>
+    <t>dfs, brute force</t>
+  </si>
+  <si>
+    <t>Sequential Digits</t>
+  </si>
+  <si>
+    <t>找范围内单调一格递增的数</t>
+  </si>
+  <si>
+    <t>这样的数一定出现在'123456789'的一段，遍历就可以</t>
+  </si>
+  <si>
+    <t>Capitalize the Title</t>
+  </si>
+  <si>
+    <t>A Number After a Double Reversal</t>
+  </si>
+  <si>
+    <t>Detect Capital</t>
+  </si>
+  <si>
+    <t>Goldman Sachs, Citadel</t>
+  </si>
+  <si>
+    <t>Goldman Sachs, Two Sigma</t>
+  </si>
+  <si>
+    <t>Akuna</t>
+  </si>
+  <si>
+    <t>Sort Integers by The Power Value</t>
+  </si>
+  <si>
+    <t>Two Sigma</t>
+  </si>
+  <si>
+    <t>Maximum Product Subarray</t>
+  </si>
+  <si>
+    <t>Shuffle an Array</t>
+  </si>
+  <si>
+    <t>Implement Rand10() Using Rand7()</t>
+  </si>
+  <si>
+    <t>Valid Mountain Array</t>
+  </si>
+  <si>
+    <t>All Elements in Two Binary Search Trees</t>
+  </si>
+  <si>
+    <t>stack, dfs</t>
+  </si>
+  <si>
+    <t>按顺序排两个tree的值</t>
+  </si>
+  <si>
+    <t>先各自inorder取值，再merge</t>
+  </si>
+  <si>
+    <t>Keep Multiplying Found Values by Two</t>
+  </si>
+  <si>
+    <t>All Divisions With the Highest Score of a Binary Array</t>
+  </si>
+  <si>
+    <t>Find Substring With Given Hash Value</t>
+  </si>
+  <si>
+    <t>Sort Even and Odd Indices Independently</t>
+  </si>
+  <si>
+    <t>Smallest Value of the Rearranged Number</t>
+  </si>
+  <si>
+    <t>Design Bitset</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-time-to-remove-all-cars-containing-illegal-goods/discuss/1748424/Python-maximum-sum-on-subarray-explained</t>
+  </si>
+  <si>
+    <t>Minimum Time to Remove All Cars Containing Illegal Goods</t>
+  </si>
+  <si>
+    <t>可以从两边或中间删有问题的car</t>
+  </si>
+  <si>
+    <t>Sort Array By Parity</t>
+  </si>
+  <si>
+    <t>Sort Array By Parity II</t>
+  </si>
+  <si>
+    <t>分为左边，右边，中间删三个之和，问题是切在哪两个地方来划分区域。cost=len(left) + 2* count(middle, 1) + len(right) = len(left) + len(middle) + len(right) + 2*count(middle, 1) - len(middle) = n + count(middle, 1) - count(middle, 0)。发现只需要中间部分和最小就行。所以就是最大sum subarray问题</t>
+  </si>
+  <si>
+    <t>Count Operations to Obtain Zero</t>
+  </si>
+  <si>
+    <t>Minimum Operations to Make the Array Alternating</t>
+  </si>
+  <si>
+    <t>Removing Minimum Number of Magic Beans</t>
+  </si>
+  <si>
+    <t>Cells in a Range on an Excel Sheet</t>
+  </si>
+  <si>
+    <t>Append K Integers With Minimal Sum</t>
+  </si>
+  <si>
+    <t>Create Binary Tree From Descriptions</t>
   </si>
   <si>
     <t>Floyd's Tortoise and Hare，相当于cycle是否存在问题
 https://blog.csdn.net/u013832707/article/details/103469112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Valid Parentheses</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Min Stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要getMin也要O(1)，就不可以用heap，binary search tree。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用另外一个stack记录到这一层为止的min_val。只要最上面的值不变，下面每一层的min_val都是不变的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Decode String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Calculator</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack记录括号外</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack记录括号外，很多特殊情况</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Calculator II</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全用stack。每个符号都先pop，计算，再push</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Daily Temperatures</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trapping Rain Water</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存多少水取决于左边的max，右边的max。从左扫一遍cummax，left_max；从右扫一遍cummax，right_max。水量就是min(left_max[i,] righ_max[i])-val[i]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remove All Adjacent Duplicates in String II</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Moving Average from Data Stream</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>queue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implement Queue using Stacks</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pop Time complexity: Amortized O(1), Worst-case O(n).
-两个stack，一个正常push，需要pop的话，就把stack1倒到stack2，然后stack2去pop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Validate Binary Search Tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree, dfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>recursive看每个node是不是binary tree。把每个recurve的结果保存最大，最小值，上浮和node比较</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Binary Tree Level Order Traversal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree, bfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Top K Frequent Elements</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用Counter，再heapq.nlargest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>python用Counter里的most_common</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remove Nth Node From End of List</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list, two pointers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遍历一遍计list长度，再遍历一遍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每次用stack，再pop N个</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>两个指针，第一个永远比第二个多N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Delete Node in a Linked List</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单向链表，不知道前一个node，所以只能把下一个node值填过来，然后把下一个node删掉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sliding Window Maximum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heap, sliding window, deque</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用heap，那么heap[0]就是最大值，但是heap插入是nlog(n)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dp[i]=min(dp[i-coin1], dp[i-coin2], …)+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.csdn.net/sinat_15723179/article/details/82183985</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merge Two Binary Trees</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>recursive, dfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest Common Prefix    </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Serialize and Deserialize Binary Tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有限制顺序，所以可以bfs也可以dfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Search a 2D Matrix II</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>divide and conquer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>左下角扫到右上角</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lowest Common Ancestor of a Binary Tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dfs遍历树，记录p,q两点的路径。再抽取相同路径。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>K Closest Points to Origin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heap, sort, divide and conquer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack用来bfs遍历树，dict用来存node-parent(node)的关系。然后找出p的所有parent放在set里。然后找q的parent直到也出现在p的parent里。这时候的q就是。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>heap.nsmallest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>divide and conquer，快排的partition方法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Minimum Remove to Make Valid Parentheses</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack放括号，剩下的是需要删除的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>two pointers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sliding window</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>binary search tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Copy List with Random Pointer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当做图一个个节点，然后遍历。遍历过的新节点就放起来。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Search a 2D Matrix</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Delete Node in a BST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reverse Words in a String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>database</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Combine Two Tables</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>left join</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>two pointers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3Sum With Multiplicity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Counter，然后分情况计数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Find Smallest Common Element in All Rows</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash table, binary search</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个row都放在set里，intersection取最小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Advantage Shuffle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>array, greedy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pacific Atlantic Water Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dfs, bfs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>medium</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Add Two Numbers II</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deque实现bfs，从边缘点bfs比边缘点大的。分pacific, atlantic找，最后intersection就是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merge k Sorted Lists</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>两两比较，比较k-1次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Subtree of Another Tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看当前是不是isMatch(),递归s的左右节点看是不是isSubtree()。isMatch()也递归的比较</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list, heap, divide and conquer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remove Linked List Elements</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注意连续满足条件的情况，只有不删除时候才curr=curr.next</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Intersection of Two Linked Lists</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用set</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list, hash table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先把list上每个node复制，跟在后面，再复制random指针，再拆分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不给head，给被删的node</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先reverse再，像第二题一样add，再reverse。reverse list的写法熟练。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>green frequent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yellow frequent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blue frequent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack, two pointers, dp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack里还要能O(1)取到最小值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用stack实现queue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连续凑够k个字母就删掉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack每个元素存（字母，累积数目）的配对</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>array</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先遍历一遍知道长度，再stack做法。空间O(n)。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先翻转左边链表，再两个指针不停next对比。空间O(1)。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>review</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>某个点开始两个list汇成一个list，找到那个点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看list有没有cycle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>复制list，且有random指针</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去掉倒数第N个节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>两个list表示两个数从个位开始，相加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去掉所有特定值的节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list翻转</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1,n]范围内取n+1个数字，找重复的那个数字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sorted array里找数字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从左上角到右下单调增，每行第一个比上一行最后一个大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>把整个矩阵当做一个单调序列，还是普通binary search。只是中点元素是哪个需要算一下对应到矩阵里。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每行都单调增，找各行交集的最小值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不重复的最长子序列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stack里记录的值肯定是单调减的。stack记录loc和value。有new high就把stack pop一遍，直到没有new high。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看简便做法板子，四步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有和是target的三个数的总数，多次出现算多次</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个矩阵从左往右递增，从上往下递增；给定个数，判断这个数出不出现。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>binary search</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remove Element</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>array, two pointers</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不使用额外空间删除list里元素。顺序无所谓。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>双指针，一个拖后写有效值，一个判断是不是val。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>K-th Element of Two Sorted Arrays</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.geeksforgeeks.org/k-th-element-two-sorted-arrays/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brick Wall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多少墙板穿不过去</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最少能凑够数额的硬币数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maximum Subarray</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Design HashMap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>easy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>linked list, array, hash table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>整数key实现hashmap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hash function用modulo，collision用array。平均O(1)，最差O(n)。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>算法导论第11章</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这题用direct address table也可以。就是memory占用更多。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power of Two</t>
-  </si>
-  <si>
-    <t>easy</t>
-  </si>
-  <si>
-    <t>math</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>Longest Common Subsequence</t>
-  </si>
-  <si>
-    <t>dp</t>
-  </si>
-  <si>
-    <t>两个字符串找最长公共子序列</t>
-  </si>
-  <si>
-    <t>初始化dp时候注意不要浅拷贝</t>
-  </si>
-  <si>
-    <t>Contains Duplicate</t>
-  </si>
-  <si>
-    <t>n &amp; (n-1) == 0</t>
-  </si>
-  <si>
-    <t>看一个数是否是2的次方</t>
-  </si>
-  <si>
-    <t>hash table</t>
-  </si>
-  <si>
-    <t>是否存在重复数</t>
-  </si>
-  <si>
-    <t>寻找sum最大连续子序列</t>
-  </si>
-  <si>
-    <t>Divide Two Integers</t>
-  </si>
-  <si>
-    <t>Multiply Strings</t>
-  </si>
-  <si>
-    <t>Add Strings</t>
-  </si>
-  <si>
-    <t>Find Nearest Point That Has the Same X or Y Coordinate</t>
-  </si>
-  <si>
-    <t>Median of Two Sorted Arrays</t>
-  </si>
-  <si>
-    <t>hard</t>
-  </si>
-  <si>
-    <t>Maximum Subarray</t>
-  </si>
-  <si>
-    <t>LRU</t>
-  </si>
-  <si>
-    <t>Find the Closest Palindrome</t>
-  </si>
-  <si>
-    <t>Design Circular Queue</t>
-  </si>
-  <si>
-    <t>array, queue</t>
-  </si>
-  <si>
-    <t>self.headIndex + self.count) % self.capacity用来描述新的head对应的queue的位置。随着head一栋，所有位置都用相对head的位置来描述。</t>
-  </si>
-  <si>
-    <t>Walls and Gates</t>
-  </si>
-  <si>
-    <t>bfs</t>
-  </si>
-  <si>
-    <t>matrix里填空白地方到最近gate的距离</t>
-  </si>
-  <si>
-    <t>Number of Islands</t>
-  </si>
-  <si>
-    <t>bfs, dfs</t>
-  </si>
-  <si>
-    <t>matrix有陆地有水，数有多少块陆地被水隔开</t>
-  </si>
-  <si>
-    <t>Sort the Matrix Diagonally</t>
-  </si>
-  <si>
-    <t>Squarepoint</t>
-  </si>
-  <si>
-    <t>每条对角线排序。字典存diagonal更快，key是row-col，value是一个list</t>
-  </si>
-  <si>
-    <t>Longest Increasing Subsequence</t>
-  </si>
-  <si>
-    <t>binary search, dp</t>
-  </si>
-  <si>
-    <t>solution里有dp教学</t>
-  </si>
-  <si>
-    <t>dp得到答案o(n^2)，更新每个dp时候需要和所有之前的dp比</t>
-  </si>
-  <si>
-    <t>Check if Every Row and Column Contains All Numbers</t>
-  </si>
-  <si>
-    <t>hash table存每行每列出现个数，最后看个数是不是1</t>
-  </si>
-  <si>
-    <t>Matrix Diagonal Sum</t>
-  </si>
-  <si>
-    <t>Valid Sudoku</t>
-  </si>
-  <si>
-    <t>同2133，hash table存每行每列每块出现个数，最后看个数是不是&lt;=1</t>
-  </si>
-  <si>
-    <t>Perfect Squares</t>
-  </si>
-  <si>
-    <t>给定的数，最少需要多少个完全平方数可以加和组成</t>
-  </si>
-  <si>
-    <t>dp, bfs</t>
-  </si>
-  <si>
-    <t>dp[i]=min(dp[i],dp[i-square]+1)。遍历square nums，而不是所有组合，减少复杂度</t>
-  </si>
-  <si>
-    <t>Flood Fill</t>
-  </si>
-  <si>
-    <t>dfs, bfs</t>
-  </si>
-  <si>
-    <t>Keys and Rooms</t>
-  </si>
-  <si>
-    <t>01 Matrix</t>
-  </si>
-  <si>
-    <t>Implement Stack using Queues</t>
-  </si>
-  <si>
-    <t>queue</t>
-  </si>
-  <si>
-    <t>一个queue。push时候新的放在前面，旧的全部push一遍。</t>
-  </si>
-  <si>
-    <t>Open the Lock</t>
-  </si>
-  <si>
-    <t>bfs, hash table</t>
-  </si>
-  <si>
-    <t>转密码锁但不能碰到一些数字，找shortest path</t>
-  </si>
-  <si>
-    <t>每个组合当做graph上面的一个node，可以转一次得到的node之间有edge。然后是bfs找shortest path</t>
-  </si>
-  <si>
-    <t>Single Number</t>
-  </si>
-  <si>
-    <t>Happy Number</t>
-  </si>
-  <si>
-    <t>hash table, two pointers</t>
-  </si>
-  <si>
-    <t>看是happy number还是无限循环</t>
-  </si>
-  <si>
-    <t>Design Linked List</t>
-  </si>
-  <si>
-    <t>linked list</t>
-  </si>
-  <si>
-    <t>Evaluate Reverse Polish Notation</t>
-  </si>
-  <si>
-    <t>stack</t>
-  </si>
-  <si>
-    <t>Clone Graph</t>
-  </si>
-  <si>
-    <t>bfs, dfs, hash table</t>
-  </si>
-  <si>
-    <t>Target Sum</t>
-  </si>
-  <si>
-    <t>[0,0,0,0,0,0,0,0,1]\n 1\n</t>
-  </si>
-  <si>
-    <t>recursion，但hash table记录visited避免重复计算</t>
-  </si>
-  <si>
-    <t>dp, hash table, backtracking</t>
-  </si>
-  <si>
-    <t>Binary Tree Inorder Traversal</t>
-  </si>
-  <si>
-    <t>dfs, stack, binary tree</t>
-  </si>
-  <si>
-    <t>中序遍历，left-mid-right</t>
-  </si>
-  <si>
-    <t>每个新node，split成[left, node, right]。stack里再多记录node是否split过。split过可以加到result，否则继续留着等split。</t>
-  </si>
-  <si>
-    <t>所有gate同时开始bfs填距离，先填距离的一定是最短的距离。天然不用存visited情况，因为empty相当于记录了。看距离，所以也只能用bfs不能用dfs。</t>
-  </si>
-  <si>
-    <t>陆地到海边的距离</t>
-  </si>
-  <si>
-    <t>每次海向内陆淹一公里，并填新的距离。用queue填海边borders，bfs。</t>
-  </si>
-  <si>
-    <t>Floyd's Tortoise and Hare，相当于找cycle起点问题
-https://blog.csdn.net/u013832707/article/details/103469112</t>
-  </si>
-  <si>
-    <t>Linked List Cycle II</t>
-  </si>
-  <si>
-    <t>linked list, hash table, two pointers</t>
-  </si>
-  <si>
-    <t>先A链存set，再B链看是否in set</t>
-  </si>
-  <si>
-    <t>cycle找起点</t>
-  </si>
-  <si>
-    <t>Odd Even Linked List</t>
-  </si>
-  <si>
-    <t>linked list, two pointers</t>
-  </si>
-  <si>
-    <t>奇数全放左边，偶数全放右边</t>
-  </si>
-  <si>
-    <t>two pointer，slow记录最后一个奇数，fast遍历list</t>
-  </si>
-  <si>
-    <t>linked list, stack</t>
-  </si>
-  <si>
-    <t>Rotate List</t>
-  </si>
-  <si>
-    <t>list保持顺序进行rotate</t>
-  </si>
-  <si>
-    <t>先生成cycle，再cut</t>
-  </si>
-  <si>
-    <t>Insert into a Sorted Circular Linked List</t>
-  </si>
-  <si>
-    <t>Flatten a Multilevel Doubly Linked List</t>
-  </si>
-  <si>
-    <t>linked list, dfs</t>
-  </si>
-  <si>
-    <t>带child指针的多层linked list flatten</t>
-  </si>
-  <si>
-    <t>用stack</t>
-  </si>
-  <si>
-    <t>Divide a String Into Groups of Size k</t>
-  </si>
-  <si>
-    <t>Minimum Moves to Reach Target Score</t>
-  </si>
-  <si>
-    <t>Solving Questions With Brainpower</t>
-  </si>
-  <si>
-    <t>Maximum Running Time of N Computers</t>
-  </si>
-  <si>
-    <t>Maximize Distance to Closest Person</t>
-  </si>
-  <si>
-    <t>找座位尽量和别人离的远</t>
-  </si>
-  <si>
-    <t>Game Play Analysis I</t>
-  </si>
-  <si>
-    <t>每个player第一次登陆日期</t>
-  </si>
-  <si>
-    <t>group by player_id后去登陆日期min</t>
-  </si>
-  <si>
-    <t>Game Play Analysis II</t>
-  </si>
-  <si>
-    <t>每个player第一次登陆日期对应的device</t>
-  </si>
-  <si>
-    <t>where的pair用法</t>
-  </si>
-  <si>
-    <t>Word Pattern</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/maximum-running-time-of-n-computers/discuss/1692939/JavaC%2B%2BPython-Sort-Solution-with-Explanation-O(mlogm)</t>
-  </si>
-  <si>
-    <t>https://leetcode-cn.com/problems/maximum-running-time-of-n-computers/solution/liang-chong-jie-fa-er-fen-da-an-pai-xu-t-grd8/</t>
-  </si>
-  <si>
-    <t>upper bound=sum(A)//n。超过平均值的，那些电池给一个电脑从头用到尾，所以不考虑这个电脑也不考虑这个电池。
-当最大的都不够平均值，那么答案就是剩下的所有电池混用能够维持的最大时间。</t>
-  </si>
-  <si>
-    <t>Can Place Flowers</t>
-  </si>
-  <si>
-    <t>Isomorphic Strings</t>
-  </si>
-  <si>
-    <t>Minimum Index Sum of Two Lists</t>
-  </si>
-  <si>
-    <t>First Unique Character in a String</t>
-  </si>
-  <si>
-    <t>Contains Duplicate II</t>
-  </si>
-  <si>
-    <t>Logger Rate Limiter</t>
-  </si>
-  <si>
-    <t>Group Anagrams</t>
-  </si>
-  <si>
-    <t>key存字符串排序</t>
-  </si>
-  <si>
-    <t>Anagrams字母只有顺序不同</t>
-  </si>
-  <si>
-    <t>Group Shifted Strings</t>
-  </si>
-  <si>
-    <t>字符串平移的合并为一组</t>
-  </si>
-  <si>
-    <t>用ord字符串diff的和拼成key。字符串zfill，自动补零。</t>
-  </si>
-  <si>
-    <t>Find Duplicate Subtrees</t>
-  </si>
-  <si>
-    <t>遍历tree，subtree序列化成字符串存到dict里</t>
-  </si>
-  <si>
-    <t>hash table, sliding window, two pointers</t>
-  </si>
-  <si>
-    <t>two pointers做</t>
-  </si>
-  <si>
-    <t>4Sum II</t>
-  </si>
-  <si>
-    <t>四个都加是n^4。先加前两个，再加后两个。再two sum。那就是n^2。</t>
-  </si>
-  <si>
-    <t>四个数的sum为target</t>
-  </si>
-  <si>
-    <t>Unique Word Abbreviation</t>
-  </si>
-  <si>
-    <t>Insert Delete GetRandom O(1)</t>
-  </si>
-  <si>
-    <t>hash table, design</t>
-  </si>
-  <si>
-    <t>同时时间insert, delete, getrandom的O(1)操作</t>
-  </si>
-  <si>
-    <t>元素存list里，dict里存val:index，这样可以delete常数。</t>
-  </si>
-  <si>
-    <t>Guess Number Higher or Lower</t>
-  </si>
-  <si>
-    <t>binary search</t>
-  </si>
-  <si>
-    <t>api版的猜数</t>
-  </si>
-  <si>
-    <t>Search in Rotated Sorted Array</t>
-  </si>
-  <si>
-    <t>list增序，但旋转几位</t>
-  </si>
-  <si>
-    <t>先binary search出start_index，再search出value</t>
-  </si>
-  <si>
-    <t>House Robber</t>
-  </si>
-  <si>
-    <t>强盗按顺序抢房子里钱，不能抢相邻的。</t>
-  </si>
-  <si>
-    <t>Min Cost Climbing Stairs</t>
-  </si>
-  <si>
-    <t>backtracking，bp</t>
-  </si>
-  <si>
-    <t>back，bp</t>
-  </si>
-  <si>
-    <t>从后向前，bp</t>
-  </si>
-  <si>
-    <t>按顺序做题，可以选择跳题，每解一题，就必须要有一些题跳过</t>
-  </si>
-  <si>
-    <t>N-th Tribonacci Number</t>
-  </si>
-  <si>
-    <t>三数相加fibonacci</t>
-  </si>
-  <si>
-    <t>Delete and Earn</t>
-  </si>
-  <si>
-    <t>同198类似</t>
-  </si>
-  <si>
-    <t>一个数选了，那前后1格数字都不能选</t>
-  </si>
-  <si>
-    <t>Koko Eating Bananas</t>
-  </si>
-  <si>
-    <t>Maximum Score from Performing Multiplication Operations</t>
-  </si>
-  <si>
-    <t>Maximal Square</t>
-  </si>
-  <si>
-    <t>找最大的全是1的方块，求面积</t>
-  </si>
-  <si>
-    <t>dp[i,j]=[i,j]作为终点的最大的全是1方块</t>
-  </si>
-  <si>
-    <t>DP[i][j] represents the longest common subsequence of text1[0 ... i] &amp; text2[0 ... j].dp[i][j] = dp[i – 1][j – 1] + 1 if text1[i – 1] == text2[j – 1] else max(dp[i][j – 1], dp[i – 1][j])</t>
-  </si>
-  <si>
-    <t>Find if Path Exists in Graph</t>
-  </si>
-  <si>
-    <t>看图上两点是否相连</t>
-  </si>
-  <si>
-    <t>stack每格存(path, visited)</t>
-  </si>
-  <si>
-    <t>stack每格存(curr_node)，有公共的visited set</t>
-  </si>
-  <si>
-    <t>All Paths From Source to Target</t>
-  </si>
-  <si>
-    <t>找图上两点间所有path</t>
-  </si>
-  <si>
-    <t>复制一个graph</t>
-  </si>
-  <si>
-    <t>有个dict存旧node和新node的关系，再dfs</t>
-  </si>
-  <si>
-    <t>Reconstruct Itinerary</t>
-  </si>
-  <si>
-    <t>Number of Connected Components in an Undirected Graph</t>
-  </si>
-  <si>
-    <t>有多少个连接块</t>
-  </si>
-  <si>
-    <t>Number of Provinces</t>
-  </si>
-  <si>
-    <t>同323</t>
-  </si>
-  <si>
-    <t>Count Elements With Strictly Smaller and Greater Elements</t>
-  </si>
-  <si>
-    <t>Rearrange Array Elements by Sign</t>
-  </si>
-  <si>
-    <t>Find All Lonely Numbers in the Array</t>
-  </si>
-  <si>
-    <t>Maximum Good People Based on Statements</t>
-  </si>
-  <si>
-    <t>dfs遍历所有可能，暴力检查</t>
-  </si>
-  <si>
-    <t>n个人互相说真假，最多多少人说真话</t>
-  </si>
-  <si>
-    <t>dfs, brute force</t>
-  </si>
-  <si>
-    <t>Sequential Digits</t>
-  </si>
-  <si>
-    <t>找范围内单调一格递增的数</t>
-  </si>
-  <si>
-    <t>这样的数一定出现在'123456789'的一段，遍历就可以</t>
-  </si>
-  <si>
-    <t>Capitalize the Title</t>
-  </si>
-  <si>
-    <t>A Number After a Double Reversal</t>
-  </si>
-  <si>
-    <t>Detect Capital</t>
-  </si>
-  <si>
-    <t>Goldman Sachs, Citadel</t>
-  </si>
-  <si>
-    <t>Goldman Sachs, Two Sigma</t>
-  </si>
-  <si>
-    <t>Akuna</t>
-  </si>
-  <si>
-    <t>Sort Integers by The Power Value</t>
-  </si>
-  <si>
-    <t>Two Sigma</t>
-  </si>
-  <si>
-    <t>Maximum Product Subarray</t>
-  </si>
-  <si>
-    <t>Shuffle an Array</t>
-  </si>
-  <si>
-    <t>Implement Rand10() Using Rand7()</t>
-  </si>
-  <si>
-    <t>Valid Mountain Array</t>
-  </si>
-  <si>
-    <t>All Elements in Two Binary Search Trees</t>
-  </si>
-  <si>
-    <t>stack, dfs</t>
-  </si>
-  <si>
-    <t>按顺序排两个tree的值</t>
-  </si>
-  <si>
-    <t>先各自inorder取值，再merge</t>
-  </si>
-  <si>
-    <t>Keep Multiplying Found Values by Two</t>
-  </si>
-  <si>
-    <t>All Divisions With the Highest Score of a Binary Array</t>
-  </si>
-  <si>
-    <t>Find Substring With Given Hash Value</t>
-  </si>
-  <si>
-    <t>2月</t>
-  </si>
-  <si>
-    <t>1月</t>
-  </si>
-  <si>
-    <t>收益</t>
-  </si>
-  <si>
-    <t>本金</t>
-  </si>
-  <si>
-    <t>Sort Even and Odd Indices Independently</t>
-  </si>
-  <si>
-    <t>Smallest Value of the Rearranged Number</t>
-  </si>
-  <si>
-    <t>Design Bitset</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/minimum-time-to-remove-all-cars-containing-illegal-goods/discuss/1748424/Python-maximum-sum-on-subarray-explained</t>
-  </si>
-  <si>
-    <t>Minimum Time to Remove All Cars Containing Illegal Goods</t>
-  </si>
-  <si>
-    <t>可以从两边或中间删有问题的car</t>
-  </si>
-  <si>
-    <t>Sort Array By Parity</t>
-  </si>
-  <si>
-    <t>Sort Array By Parity II</t>
-  </si>
-  <si>
-    <t>分为左边，右边，中间删三个之和，问题是切在哪两个地方来划分区域。cost=len(left) + 2* count(middle, 1) + len(right) = len(left) + len(middle) + len(right) + 2*count(middle, 1) - len(middle) = n + count(middle, 1) - count(middle, 0)。发现只需要中间部分和最小就行。所以就是最大sum subarray问题</t>
-  </si>
-  <si>
-    <t>Count Operations to Obtain Zero</t>
-  </si>
-  <si>
-    <t>Minimum Operations to Make the Array Alternating</t>
-  </si>
-  <si>
-    <t>Removing Minimum Number of Magic Beans</t>
-  </si>
-  <si>
-    <t>Cells in a Range on an Excel Sheet</t>
-  </si>
-  <si>
-    <t>Append K Integers With Minimal Sum</t>
-  </si>
-  <si>
-    <t>Create Binary Tree From Descriptions</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>存成stackA和stackB，pop直到有区别的node</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2006,7 +1994,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2033,9 +2021,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -2043,18 +2028,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2152,7 +2125,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2192,7 +2165,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2441,7 +2414,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2690,7 +2663,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2939,7 +2912,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3177,7 +3150,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3312,6 +3285,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3319,7 +3293,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3422,7 +3395,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3462,7 +3435,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3711,7 +3684,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3960,7 +3933,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -4209,7 +4182,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -4447,7 +4420,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4582,6 +4555,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4589,7 +4563,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6073,2666 +6046,2705 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B7B66D-011E-4D1B-AC2F-2C5C53A1B819}">
-  <dimension ref="A1:L157"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M157"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="9" customWidth="1"/>
-    <col min="3" max="4" width="11.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" style="9" customWidth="1"/>
-    <col min="7" max="10" width="33.42578125" style="9" customWidth="1"/>
-    <col min="11" max="12" width="9" style="9"/>
-    <col min="13" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="6.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" style="9" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="9" customWidth="1"/>
+    <col min="4" max="5" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="9" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" style="9" customWidth="1"/>
+    <col min="8" max="11" width="33.5" style="9" customWidth="1"/>
+    <col min="12" max="13" width="9" style="9"/>
+    <col min="14" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1">
+    <row r="1" spans="1:13" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="G1" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="10">
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="30">
-      <c r="A3" s="10">
+    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>271</v>
-      </c>
       <c r="G3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45">
-      <c r="A4" s="10">
+    <row r="4" spans="1:13" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>436</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>281</v>
+        <v>434</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="45">
-      <c r="A5" s="10">
+        <v>279</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="45">
-      <c r="A6" s="10">
+    <row r="6" spans="1:13" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="10">
+    </row>
+    <row r="7" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>7</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="10">
+    <row r="8" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
         <v>9</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="10">
+    <row r="9" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="30">
-      <c r="A10" s="10">
+    </row>
+    <row r="10" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
         <v>19</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="10">
+    </row>
+    <row r="11" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
         <v>20</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30">
-      <c r="A12" s="10">
+    </row>
+    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
         <v>21</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45">
-      <c r="A13" s="10">
+    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
         <v>23</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="F13" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="30">
-      <c r="A14" s="10">
+    </row>
+    <row r="14" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
         <v>27</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="45">
-      <c r="A15" s="10">
+    </row>
+    <row r="15" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="7">
         <v>33</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="30">
-      <c r="A16" s="10">
+    </row>
+    <row r="16" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
         <v>34</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="60">
-      <c r="A17" s="10">
+    <row r="17" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>319</v>
+        <v>348</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="75">
-      <c r="A18" s="10">
+        <v>317</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
         <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30">
-      <c r="A19" s="10">
+      <c r="F18" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
         <v>49</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="30">
-      <c r="A20" s="10">
+      <c r="H19" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
         <v>50</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="17" customFormat="1" ht="30">
-      <c r="A21" s="10">
+    <row r="21" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
         <v>53</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="10">
+      <c r="B21" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
         <v>55</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="30">
-      <c r="A23" s="10">
+    <row r="23" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7">
         <v>56</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="30">
-      <c r="A24" s="10">
+    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="7">
         <v>61</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="10">
+    </row>
+    <row r="25" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
         <v>69</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="H25" s="9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="60">
-      <c r="A26" s="10">
+    <row r="26" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7">
         <v>74</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E26" s="9" t="s">
+      <c r="F26" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>277</v>
-      </c>
       <c r="G26" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="30">
-      <c r="A27" s="10">
+        <v>275</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="7">
         <v>83</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60">
-      <c r="A28" s="10">
+    <row r="28" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="7">
         <v>94</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="G28" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="45">
-      <c r="A29" s="10">
+    </row>
+    <row r="29" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="7">
         <v>98</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="F29" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="H29" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="G29" s="9" t="s">
+    </row>
+    <row r="30" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7">
+        <v>102</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="30">
-      <c r="A30" s="10">
-        <v>102</v>
-      </c>
-      <c r="B30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="F30" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="10">
+    </row>
+    <row r="31" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7">
         <v>121</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="D31" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="H31" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="30">
-      <c r="A32" s="10">
+    <row r="32" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7">
         <v>133</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>476</v>
+        <v>374</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="10">
+        <v>474</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7">
         <v>136</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="30">
-      <c r="A34" s="10">
+        <v>365</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="7">
         <v>138</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="60">
-      <c r="A35" s="10">
+    </row>
+    <row r="35" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A35" s="7">
         <v>141</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>250</v>
-      </c>
       <c r="F35" s="9" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="60">
-      <c r="A36" s="10">
+      <c r="I35" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A36" s="7">
         <v>142</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E36" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="60">
-      <c r="A37" s="10">
+      <c r="H36" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7">
         <v>146</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="H37" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30">
-      <c r="A38" s="10">
+    <row r="38" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="7">
         <v>150</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="C38" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="7">
+        <v>151</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="15">
+        <v>152</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="7">
+        <v>155</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A42" s="7">
+        <v>160</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="9">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="7">
+        <v>175</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="7">
+        <v>198</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F44" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="10">
-        <v>151</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="20">
-        <v>152</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="60">
-      <c r="A41" s="10">
-        <v>155</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="30">
-      <c r="A42" s="10">
-        <v>160</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="G44" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="7">
+        <v>200</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="7">
+        <v>202</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A47" s="7">
+        <v>203</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" s="9">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E42" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="10">
-        <v>175</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="30">
-      <c r="A44" s="10">
-        <v>198</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30">
-      <c r="A45" s="10">
-        <v>200</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30">
-      <c r="A46" s="10">
-        <v>202</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="30">
-      <c r="A47" s="10">
-        <v>203</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="10">
+    </row>
+    <row r="48" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7">
         <v>205</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="10">
+        <v>421</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="7">
         <v>206</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="9">
+        <v>1</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="G49" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="10">
+        <v>271</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7">
         <v>217</v>
       </c>
       <c r="B50" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="7">
+        <v>219</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="7">
+        <v>221</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="7">
+        <v>224</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7">
+        <v>225</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7">
+        <v>227</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="7">
+        <v>231</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="10">
-        <v>219</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="30">
-      <c r="A52" s="10">
-        <v>221</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="10">
-        <v>224</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="30">
-      <c r="A54" s="10">
-        <v>225</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="30">
-      <c r="A55" s="10">
-        <v>227</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="10">
-        <v>231</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="75">
-      <c r="A57" s="10">
+      <c r="H56" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="7">
         <v>232</v>
       </c>
       <c r="B57" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="F57" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="G57" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="30">
-      <c r="A58" s="10">
+    </row>
+    <row r="58" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A58" s="7">
         <v>234</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="9">
+        <v>1</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E58" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>264</v>
+      <c r="F58" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="90">
-      <c r="A59" s="10">
+        <v>262</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7">
         <v>236</v>
       </c>
       <c r="B59" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E59" s="9" t="s">
+      <c r="H59" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="G59" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="45">
-      <c r="A60" s="10">
+      <c r="I59" s="9" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A60" s="7">
         <v>237</v>
       </c>
       <c r="B60" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="9">
+        <v>1</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="F60" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="G60" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="H60" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="G60" s="9" t="s">
+    </row>
+    <row r="61" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7">
+        <v>239</v>
+      </c>
+      <c r="B61" s="9" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="30">
-      <c r="A61" s="10">
-        <v>239</v>
-      </c>
-      <c r="B61" s="9" t="s">
+      <c r="D61" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="F61" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="G61" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="60">
-      <c r="A62" s="10">
+      <c r="I61" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7">
         <v>240</v>
       </c>
       <c r="B62" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="F62" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="G62" s="9" t="s">
+      <c r="I62" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="H62" s="9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="30">
-      <c r="A63" s="10">
+    </row>
+    <row r="63" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7">
         <v>249</v>
       </c>
       <c r="B63" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="10">
+    </row>
+    <row r="64" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7">
         <v>278</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="9" t="s">
+      <c r="F64" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="H64" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="60">
-      <c r="A65" s="10">
+    <row r="65" spans="1:11" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="7">
         <v>279</v>
       </c>
       <c r="B65" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="G65" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="G65" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="75">
-      <c r="A66" s="10">
+    </row>
+    <row r="66" spans="1:11" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7">
         <v>286</v>
       </c>
       <c r="B66" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="60">
-      <c r="A67" s="10">
+      <c r="H66" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7">
         <v>287</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="D67" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="F67" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>275</v>
-      </c>
       <c r="G67" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="I67" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="I67" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="J67" s="8"/>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" s="10">
+      <c r="J67" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K67" s="8"/>
+    </row>
+    <row r="68" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7">
         <v>288</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="J68" s="8"/>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" s="10">
+        <v>439</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K68" s="8"/>
+    </row>
+    <row r="69" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7">
         <v>290</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="C69" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K69" s="8"/>
+    </row>
+    <row r="70" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="7">
+        <v>297</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K70" s="8"/>
+    </row>
+    <row r="71" spans="1:11" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="7">
+        <v>300</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="J69" s="8"/>
-    </row>
-    <row r="70" spans="1:10" ht="30">
-      <c r="A70" s="10">
-        <v>297</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="J70" s="8"/>
-    </row>
-    <row r="71" spans="1:10" ht="30">
-      <c r="A71" s="10">
-        <v>300</v>
-      </c>
-      <c r="B71" s="9" t="s">
+      <c r="E71" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="E71" s="9" t="s">
+      <c r="H71" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="J71" s="8"/>
-    </row>
-    <row r="72" spans="1:10" ht="30">
-      <c r="A72" s="10">
+      <c r="K71" s="8"/>
+    </row>
+    <row r="72" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7">
         <v>322</v>
       </c>
       <c r="B72" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="D72" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E72" s="9" t="s">
-        <v>139</v>
-      </c>
       <c r="F72" s="9" t="s">
-        <v>298</v>
+        <v>138</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="J72" s="8"/>
-    </row>
-    <row r="73" spans="1:10" ht="45">
-      <c r="A73" s="10">
+        <v>296</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K72" s="8"/>
+    </row>
+    <row r="73" spans="1:11" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="7">
         <v>323</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>357</v>
+        <v>477</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>309</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="J73" s="8"/>
-    </row>
-    <row r="74" spans="1:10" ht="45">
-      <c r="A74" s="10">
+        <v>355</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="K73" s="8"/>
+    </row>
+    <row r="74" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="A74" s="7">
         <v>328</v>
       </c>
       <c r="B74" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G74" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E74" s="9" t="s">
+      <c r="H74" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="J74" s="8"/>
-    </row>
-    <row r="75" spans="1:10">
-      <c r="A75" s="10">
+      <c r="K74" s="8"/>
+    </row>
+    <row r="75" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="7">
         <v>332</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="J75" s="8"/>
-    </row>
-    <row r="76" spans="1:10" ht="30">
-      <c r="A76" s="10">
+        <v>476</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="K75" s="8"/>
+    </row>
+    <row r="76" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="7">
         <v>346</v>
       </c>
       <c r="B76" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="D76" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="F76" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E76" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J76" s="8"/>
-    </row>
-    <row r="77" spans="1:10" ht="30">
-      <c r="A77" s="10">
+      <c r="K76" s="8"/>
+    </row>
+    <row r="77" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="7">
         <v>347</v>
       </c>
       <c r="B77" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="H77" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="J77" s="8"/>
-    </row>
-    <row r="78" spans="1:10">
-      <c r="A78" s="10">
+      <c r="I77" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="K77" s="8"/>
+    </row>
+    <row r="78" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="7">
         <v>349</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E78" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" s="10">
+      <c r="F78" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="7">
         <v>350</v>
       </c>
       <c r="B79" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="D79" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="G79" s="9" t="s">
+      <c r="F79" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
-      <c r="A80" s="10">
+    <row r="80" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="7">
         <v>359</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="C80" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="7">
+        <v>374</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="7">
+        <v>380</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E80" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="10">
+      <c r="F82" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="15">
+        <v>384</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="7">
+        <v>387</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="7">
+        <v>394</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="7">
+        <v>417</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A87" s="7">
+        <v>430</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A88" s="7">
+        <v>445</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="7">
+        <v>450</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="7">
+        <v>454</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="15">
+        <v>470</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="7">
+        <v>494</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="7">
+        <v>520</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="7">
+        <v>542</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="7">
+        <v>547</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="7">
+        <v>554</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="7">
+        <v>572</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="7">
+        <v>599</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="7">
+        <v>605</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="7">
+        <v>617</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="64" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="7">
+        <v>622</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="7">
+        <v>652</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F102" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="30">
-      <c r="A82" s="10">
-        <v>380</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="20">
-        <v>384</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="10">
-        <v>387</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="10">
-        <v>394</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="45">
-      <c r="A86" s="10">
-        <v>417</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="30">
-      <c r="A87" s="10">
-        <v>430</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="45">
-      <c r="A88" s="10">
-        <v>445</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E88" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="10">
-        <v>450</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="45">
-      <c r="A90" s="10">
-        <v>454</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="30">
-      <c r="A91" s="20">
-        <v>470</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="30">
-      <c r="A92" s="10">
-        <v>494</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="10">
-        <v>520</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="45">
-      <c r="A94" s="10">
-        <v>542</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="10">
-        <v>547</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="10">
-        <v>554</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="45">
-      <c r="A97" s="10">
-        <v>572</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="30">
-      <c r="A98" s="10">
-        <v>599</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="10">
-        <v>605</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="10">
-        <v>617</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="75">
-      <c r="A101" s="10">
-        <v>622</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="30">
-      <c r="A102" s="10">
-        <v>652</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E102" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9">
-      <c r="A103" s="10">
+      <c r="H102" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7">
         <v>704</v>
       </c>
       <c r="B103" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="D103" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E103" s="9" t="s">
+      <c r="F103" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>276</v>
-      </c>
       <c r="G103" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="45">
-      <c r="A104" s="10">
+    <row r="104" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A104" s="7">
         <v>706</v>
       </c>
       <c r="B104" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F104" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="G104" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="E104" s="9" t="s">
+      <c r="H104" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="I104" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="J104" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="H104" s="9" t="s">
+    </row>
+    <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
+        <v>707</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A106" s="7">
+        <v>708</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="7">
+        <v>733</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="D107" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="I104" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="10">
-        <v>707</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="C105" s="8" t="s">
+      <c r="F107" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="7">
+        <v>739</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="7">
+        <v>740</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F109" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E105" s="9" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="30">
-      <c r="A106" s="10">
-        <v>708</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="C106" s="8" t="s">
+      <c r="G109" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="7">
+        <v>746</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F110" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E106" s="9" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="10">
-        <v>733</v>
-      </c>
-      <c r="B107" s="9" t="s">
+      <c r="H110" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="7">
+        <v>752</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="7">
+        <v>797</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="7">
+        <v>841</v>
+      </c>
+      <c r="B113" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="D113" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E107" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="60">
-      <c r="A108" s="10">
-        <v>739</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E108" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G108" s="9" t="s">
+      <c r="F113" s="9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="7">
+        <v>849</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="7">
+        <v>870</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="7">
+        <v>875</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="7">
+        <v>905</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="7">
+        <v>922</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="7">
+        <v>923</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G119" s="9" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="30">
-      <c r="A109" s="10">
-        <v>740</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="C109" s="8" t="s">
+      <c r="H119" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="7">
+        <v>941</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="7">
+        <v>973</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="7">
+        <v>1137</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="7">
+        <v>1143</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F123" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E109" s="9" t="s">
+      <c r="G123" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="I123" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="F109" s="9" t="s">
+    </row>
+    <row r="124" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="7">
+        <v>1198</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="7">
+        <v>1209</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="7">
+        <v>1249</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="7">
+        <v>1291</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="7">
+        <v>1305</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="7">
+        <v>1329</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="15">
+        <v>1387</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="7">
+        <v>1572</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="15">
+        <v>1770</v>
+      </c>
+      <c r="B132" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="G109" s="9" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="10">
-        <v>746</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C110" s="8" t="s">
+      <c r="D132" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="E110" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="45">
-      <c r="A111" s="10">
-        <v>752</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="C111" s="8" t="s">
+      <c r="F132" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E111" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="A112" s="10">
-        <v>797</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E112" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="10">
-        <v>841</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E113" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="30">
-      <c r="A114" s="10">
-        <v>849</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="10">
-        <v>870</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E115" s="9" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="10">
-        <v>875</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="10">
-        <v>905</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="10">
-        <v>922</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="45">
-      <c r="A119" s="10">
-        <v>923</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="10">
-        <v>941</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="30">
-      <c r="A121" s="10">
-        <v>973</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E121" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G121" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="10">
-        <v>1137</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F122" s="9" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="75">
-      <c r="A123" s="10">
-        <v>1143</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="G123" s="9" t="s">
+    </row>
+    <row r="133" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="7">
+        <v>1971</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="G133" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="H123" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="30">
-      <c r="A124" s="10">
-        <v>1198</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E124" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="30">
-      <c r="A125" s="10">
-        <v>1209</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E125" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="G125" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="30">
-      <c r="A126" s="10">
-        <v>1249</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E126" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="G126" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="30">
-      <c r="A127" s="10">
-        <v>1291</v>
-      </c>
-      <c r="B127" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F127" s="9" t="s">
+      <c r="H133" s="9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="7">
+        <v>2119</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="7">
+        <v>2129</v>
+      </c>
+      <c r="B135" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="G127" s="9" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="30">
-      <c r="A128" s="10">
-        <v>1305</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="45">
-      <c r="A129" s="10">
-        <v>1329</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="30">
-      <c r="A130" s="20">
-        <v>1387</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="10">
-        <v>1572</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="45">
-      <c r="A132" s="20">
-        <v>1770</v>
-      </c>
-      <c r="B132" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="E132" s="9" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="30">
-      <c r="A133" s="10">
-        <v>1971</v>
-      </c>
-      <c r="B133" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E133" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F133" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="30">
-      <c r="A134" s="10">
-        <v>2119</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>494</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9">
-      <c r="A135" s="10">
-        <v>2129</v>
-      </c>
-      <c r="B135" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="45">
-      <c r="A136" s="10">
+      <c r="D135" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="7">
         <v>2133</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E136" s="9" t="s">
-        <v>319</v>
+        <v>345</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>307</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="30">
+        <v>317</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>2138</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="30">
+        <v>404</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>2139</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" ht="45">
+        <v>405</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>2140</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="C139" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="F139" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="E139" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>458</v>
-      </c>
       <c r="G139" s="9" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="120">
+        <v>456</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="112" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>2141</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E140" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G140" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="H140" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="I140" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="H140" s="14" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" ht="30">
+      <c r="I140" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>2148</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="30">
+        <v>481</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>2149</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="30">
+        <v>482</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>2150</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ht="30">
+        <v>483</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>2151</v>
       </c>
       <c r="B144" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="G144" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="C144" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="G144" s="9" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="30">
+      <c r="H144" s="9" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>2154</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" ht="30">
+        <v>507</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>2155</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" ht="30">
+        <v>508</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>2156</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="30">
+        <v>509</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>2164</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" ht="30">
+        <v>510</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>2165</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H149" s="13"/>
-    </row>
-    <row r="150" spans="1:8">
+        <v>511</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I149" s="12"/>
+    </row>
+    <row r="150" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>2166</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="H150" s="13"/>
-    </row>
-    <row r="151" spans="1:8" ht="165">
+        <v>512</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I150" s="12"/>
+    </row>
+    <row r="151" spans="1:9" ht="128" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>2167</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>520</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>521</v>
+        <v>514</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>325</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="H151" s="13" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+        <v>515</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>2169</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" ht="30">
+        <v>519</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>2170</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" ht="30">
+        <v>520</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>2171</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" ht="30">
+        <v>521</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>2194</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="30">
+        <v>522</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>2195</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" ht="30">
+        <v>523</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>2196</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>311</v>
+        <v>524</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>309</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L144" xr:uid="{1C56C913-064E-423F-843C-70445A14D676}"/>
+  <autoFilter ref="A1:M157" xr:uid="{1C56C913-064E-423F-843C-70445A14D676}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="linked list"/>
+        <filter val="linked list, array, hash table"/>
+        <filter val="linked list, dfs"/>
+        <filter val="linked list, hash table"/>
+        <filter val="linked list, hash table, two pointers"/>
+        <filter val="linked list, heap, divide and conquer"/>
+        <filter val="linked list, stack"/>
+        <filter val="linked list, two pointers"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H61" r:id="rId1" xr:uid="{1A0B9458-2E5B-46D8-B44E-F8E45F0E8738}"/>
-    <hyperlink ref="F6" r:id="rId2" xr:uid="{EA113FAB-F94F-4508-8ED6-94388E6A09A7}"/>
-    <hyperlink ref="I140" r:id="rId3" xr:uid="{A363DD3B-75EA-422A-B19E-76CA6A2E19E8}"/>
-    <hyperlink ref="H151" r:id="rId4" xr:uid="{F9F4DB09-A6FA-4D22-B87C-A70C4E2A9F74}"/>
+    <hyperlink ref="I61" r:id="rId1" xr:uid="{1A0B9458-2E5B-46D8-B44E-F8E45F0E8738}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{EA113FAB-F94F-4508-8ED6-94388E6A09A7}"/>
+    <hyperlink ref="J140" r:id="rId3" xr:uid="{A363DD3B-75EA-422A-B19E-76CA6A2E19E8}"/>
+    <hyperlink ref="I151" r:id="rId4" xr:uid="{F9F4DB09-A6FA-4D22-B87C-A70C4E2A9F74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
@@ -8740,68 +8752,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5363D932-B6FD-4DDA-89F5-766FC66F4B63}">
-  <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA4FB45-65C7-4804-B2C5-A3763C8E324A}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" customWidth="1"/>
+    <col min="3" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B3">
-        <v>81.599999999999994</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>512</v>
-      </c>
-      <c r="B4">
-        <v>171.08</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B5">
-        <v>254251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="B6">
-        <f>SUM(B3:B5)</f>
-        <v>254503.67999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA4FB45-65C7-4804-B2C5-A3763C8E324A}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" customWidth="1"/>
-    <col min="7" max="7" width="31.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8818,46 +8781,46 @@
         <v>8</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" ht="30">
-      <c r="A2" s="10">
+    <row r="2" spans="1:7" s="8" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="7">
         <v>511</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>74</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="8" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>512</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>413</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" ht="30">
-      <c r="A3" s="10">
-        <v>512</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>415</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>74</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -8866,21 +8829,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8900,7 +8863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8917,7 +8880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>83</v>
       </c>
@@ -8937,7 +8900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>322</v>
       </c>
@@ -8960,7 +8923,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>443</v>
       </c>
@@ -8980,7 +8943,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>532</v>
       </c>
@@ -9003,7 +8966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>547</v>
       </c>
@@ -9017,7 +8980,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -9026,7 +8989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>647</v>
       </c>
@@ -9040,7 +9003,7 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F8" t="s">
         <v>40</v>
@@ -9049,7 +9012,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>724</v>
       </c>
@@ -9069,7 +9032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>733</v>
       </c>
@@ -9087,7 +9050,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>780</v>
       </c>
@@ -9107,7 +9070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1041</v>
       </c>
@@ -9130,7 +9093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1051</v>
       </c>
@@ -9150,7 +9113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1163</v>
       </c>
@@ -9179,15 +9142,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8661F369-1314-4056-8910-E5294C54F722}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" ht="30">
+    <row r="1" spans="1:12" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -9204,7 +9167,7 @@
         <v>8</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>97</v>
@@ -9215,34 +9178,33 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" s="15" customFormat="1">
-      <c r="A2" s="15">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="8">
         <v>4</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="D2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-    </row>
-    <row r="3" spans="1:12" s="8" customFormat="1">
-      <c r="A3" s="15">
+      <c r="B2" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+    </row>
+    <row r="3" spans="1:12" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
         <v>29</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -9252,30 +9214,30 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="15">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
         <v>56</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -9285,48 +9247,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="15">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
         <v>146</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>564</v>
       </c>
       <c r="B9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1779</v>
       </c>
       <c r="B10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -9334,26 +9296,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7C2A69-420F-4346-8F8A-01973B865F7F}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>98</v>
       </c>
@@ -9369,20 +9331,20 @@
       <c r="E1" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="11" t="str">
+      <c r="G1" s="10" t="str">
         <f>A1</f>
         <v>Date</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>109</v>
       </c>
       <c r="N1" t="s">
@@ -9392,8 +9354,8 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="11">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="10">
         <v>44197</v>
       </c>
       <c r="B2">
@@ -9409,23 +9371,23 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="10">
         <f t="shared" ref="G2:G17" si="0">A2</f>
         <v>44197</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <f t="shared" ref="H2:H17" si="1">B2/$O$1</f>
         <v>0</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <f>C2/$O$2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="11">
         <f>D2/$O$3</f>
         <v>0</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <f>E2/$O$4</f>
         <v>0</v>
       </c>
@@ -9436,8 +9398,8 @@
         <v>541</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="11">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
         <v>44258</v>
       </c>
       <c r="B3">
@@ -9453,23 +9415,23 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <f t="shared" si="0"/>
         <v>44258</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <f t="shared" si="1"/>
         <v>2.1677662582469368E-2</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <f t="shared" ref="I3:I17" si="3">C3/$O$2</f>
         <v>5.545286506469501E-2</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <f t="shared" ref="J3:J17" si="4">D3/$O$3</f>
         <v>1.048951048951049E-2</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <f t="shared" ref="K3:K17" si="5">E3/$O$4</f>
         <v>8.7336244541484712E-3</v>
       </c>
@@ -9480,8 +9442,8 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="11">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
         <v>44259</v>
       </c>
       <c r="B4">
@@ -9497,23 +9459,23 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <f t="shared" si="0"/>
         <v>44259</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <f t="shared" si="1"/>
         <v>2.35626767200754E-2</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <f t="shared" si="3"/>
         <v>6.0998151571164512E-2</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <f t="shared" si="4"/>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <f t="shared" si="5"/>
         <v>8.7336244541484712E-3</v>
       </c>
@@ -9524,8 +9486,8 @@
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="11">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
         <v>44260</v>
       </c>
       <c r="B5">
@@ -9541,29 +9503,29 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <f t="shared" si="0"/>
         <v>44260</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f t="shared" si="1"/>
         <v>2.35626767200754E-2</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f t="shared" si="3"/>
         <v>6.0998151571164512E-2</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <f t="shared" si="4"/>
         <v>1.1363636363636364E-2</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="11">
         <f t="shared" si="5"/>
         <v>8.7336244541484712E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="11">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
         <v>44263</v>
       </c>
       <c r="B6">
@@ -9579,29 +9541,29 @@
       <c r="E6">
         <v>6</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <f t="shared" si="0"/>
         <v>44263</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <f t="shared" si="1"/>
         <v>2.7332704995287466E-2</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f t="shared" si="3"/>
         <v>6.4695009242144177E-2</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <f t="shared" si="4"/>
         <v>1.486013986013986E-2</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="11">
         <f t="shared" si="5"/>
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="11">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="10">
         <v>44264</v>
       </c>
       <c r="B7">
@@ -9617,29 +9579,29 @@
       <c r="E7">
         <v>6</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <f t="shared" si="0"/>
         <v>44264</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <f t="shared" si="1"/>
         <v>2.7803958529688973E-2</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f t="shared" si="3"/>
         <v>6.6543438077634007E-2</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <f t="shared" si="4"/>
         <v>1.486013986013986E-2</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <f t="shared" si="5"/>
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="11">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
         <v>44266</v>
       </c>
       <c r="B8">
@@ -9655,29 +9617,29 @@
       <c r="E8">
         <v>6</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <f t="shared" si="0"/>
         <v>44266</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <f t="shared" si="1"/>
         <v>2.827521206409048E-2</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f t="shared" si="3"/>
         <v>6.6543438077634007E-2</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <f t="shared" si="4"/>
         <v>1.5734265734265736E-2</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <f t="shared" si="5"/>
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="11">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
         <v>44270</v>
       </c>
       <c r="B9">
@@ -9693,29 +9655,29 @@
       <c r="E9">
         <v>6</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <f t="shared" si="0"/>
         <v>44270</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>2.8746465598491987E-2</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f t="shared" si="3"/>
         <v>6.6543438077634007E-2</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <f t="shared" si="4"/>
         <v>1.6608391608391608E-2</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="11">
         <f t="shared" si="5"/>
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="11">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
         <v>44273</v>
       </c>
       <c r="B10">
@@ -9731,29 +9693,29 @@
       <c r="E10">
         <v>7</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="10">
         <f t="shared" si="0"/>
         <v>44273</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f t="shared" si="1"/>
         <v>3.0631479736098022E-2</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f t="shared" si="3"/>
         <v>7.0240295748613679E-2</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <f t="shared" si="4"/>
         <v>1.7482517482517484E-2</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <f t="shared" si="5"/>
         <v>1.5283842794759825E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="10">
         <v>44274</v>
       </c>
       <c r="B11">
@@ -9769,29 +9731,29 @@
       <c r="E11">
         <v>8</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f t="shared" si="0"/>
         <v>44274</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <f t="shared" si="1"/>
         <v>3.157398680490104E-2</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f t="shared" si="3"/>
         <v>7.0240295748613679E-2</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <f t="shared" si="4"/>
         <v>1.8356643356643356E-2</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f t="shared" si="5"/>
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="11">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="10">
         <v>44277</v>
       </c>
       <c r="B12">
@@ -9807,29 +9769,29 @@
       <c r="E12">
         <v>8</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="10">
         <f t="shared" si="0"/>
         <v>44277</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <f t="shared" si="1"/>
         <v>3.2516493873704054E-2</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f t="shared" si="3"/>
         <v>7.0240295748613679E-2</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <f t="shared" si="4"/>
         <v>2.0104895104895104E-2</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <f t="shared" si="5"/>
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="11">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="10">
         <v>44278</v>
       </c>
       <c r="B13">
@@ -9845,29 +9807,29 @@
       <c r="E13">
         <v>8</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="10">
         <f t="shared" si="0"/>
         <v>44278</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>3.5344015080113103E-2</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f t="shared" si="3"/>
         <v>7.2088724584103508E-2</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <f t="shared" si="4"/>
         <v>2.4475524475524476E-2</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <f t="shared" si="5"/>
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="11">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
         <v>44280</v>
       </c>
       <c r="B14">
@@ -9883,29 +9845,29 @@
       <c r="E14">
         <v>9</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
         <v>44280</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f t="shared" si="1"/>
         <v>3.6757775683317624E-2</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <f t="shared" si="3"/>
         <v>7.2088724584103508E-2</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <f t="shared" si="4"/>
         <v>2.6223776223776224E-2</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <f t="shared" si="5"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="11">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
         <v>44292</v>
       </c>
       <c r="B15">
@@ -9921,29 +9883,29 @@
       <c r="E15">
         <v>9</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
         <v>44292</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f t="shared" si="1"/>
         <v>3.7229029217719131E-2</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f t="shared" si="3"/>
         <v>7.3937153419593352E-2</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="11">
         <f t="shared" si="4"/>
         <v>2.6223776223776224E-2</v>
       </c>
-      <c r="K15" s="12">
+      <c r="K15" s="11">
         <f t="shared" si="5"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="11">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
         <v>44364</v>
       </c>
       <c r="B16">
@@ -9959,29 +9921,29 @@
       <c r="E16">
         <v>9</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <f t="shared" si="0"/>
         <v>44364</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f t="shared" si="1"/>
         <v>3.8171536286522152E-2</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <f t="shared" si="3"/>
         <v>7.763401109057301E-2</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <f t="shared" si="4"/>
         <v>2.6223776223776224E-2</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <f t="shared" si="5"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
         <v>44369</v>
       </c>
       <c r="B17">
@@ -9997,29 +9959,29 @@
       <c r="E17">
         <v>9</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="10">
         <f t="shared" si="0"/>
         <v>44369</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <f t="shared" si="1"/>
         <v>4.005655042412818E-2</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <f t="shared" si="3"/>
         <v>7.9482439926062853E-2</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <f t="shared" si="4"/>
         <v>2.8846153846153848E-2</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <f t="shared" si="5"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
         <v>44558</v>
       </c>
       <c r="B18">
@@ -10035,29 +9997,29 @@
       <c r="E18">
         <v>9</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="10">
         <f t="shared" ref="G18:G33" si="7">A18</f>
         <v>44558</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <f t="shared" ref="H18:H29" si="8">B18/$O$1</f>
         <v>4.2884071630537229E-2</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <f t="shared" ref="I18:I29" si="9">C18/$O$2</f>
         <v>8.1330868761552683E-2</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <f t="shared" ref="J18:J29" si="10">D18/$O$3</f>
         <v>3.3216783216783216E-2</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <f t="shared" ref="K18:K34" si="11">E18/$O$4</f>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
         <v>44571</v>
       </c>
       <c r="B19">
@@ -10073,29 +10035,29 @@
       <c r="E19">
         <v>9</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="10">
         <f t="shared" si="7"/>
         <v>44571</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <f t="shared" si="8"/>
         <v>4.71253534401508E-2</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="11">
         <f t="shared" si="9"/>
         <v>8.6876155268022184E-2</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="11">
         <f t="shared" si="10"/>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <f t="shared" si="11"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
         <v>44572</v>
       </c>
       <c r="B20">
@@ -10111,29 +10073,29 @@
       <c r="E20">
         <v>9</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="10">
         <f t="shared" si="7"/>
         <v>44572</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <f t="shared" si="8"/>
         <v>4.9481621112158342E-2</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <f t="shared" si="9"/>
         <v>9.0573012939001843E-2</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="11">
         <f t="shared" si="10"/>
         <v>4.1083916083916081E-2</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <f t="shared" si="11"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
         <v>44573</v>
       </c>
       <c r="B21">
@@ -10149,29 +10111,29 @@
       <c r="E21">
         <v>9</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="10">
         <f t="shared" si="7"/>
         <v>44573</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <f t="shared" si="8"/>
         <v>5.2780395852968898E-2</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <f t="shared" si="9"/>
         <v>9.2421441774491686E-2</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="11">
         <f t="shared" si="10"/>
         <v>4.6328671328671328E-2</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <f t="shared" si="11"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
         <v>44574</v>
       </c>
       <c r="B22">
@@ -10187,29 +10149,29 @@
       <c r="E22">
         <v>9</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="10">
         <f t="shared" si="7"/>
         <v>44574</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <f t="shared" si="8"/>
         <v>5.4194156456173419E-2</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <f t="shared" si="9"/>
         <v>9.4269870609981515E-2</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="11">
         <f t="shared" si="10"/>
         <v>4.807692307692308E-2</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <f t="shared" si="11"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" s="10">
         <v>44576</v>
       </c>
       <c r="B23">
@@ -10225,29 +10187,29 @@
       <c r="E23">
         <v>9</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="10">
         <f t="shared" si="7"/>
         <v>44576</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="11">
         <f t="shared" si="8"/>
         <v>5.5607917059377947E-2</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="11">
         <f t="shared" si="9"/>
         <v>9.6118299445471345E-2</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="11">
         <f t="shared" si="10"/>
         <v>4.9825174825174824E-2</v>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="11">
         <f t="shared" si="11"/>
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="10">
         <v>44577</v>
       </c>
       <c r="B24">
@@ -10263,29 +10225,29 @@
       <c r="E24">
         <v>10</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="10">
         <f t="shared" si="7"/>
         <v>44577</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <f t="shared" si="8"/>
         <v>5.7492931196983975E-2</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <f t="shared" si="9"/>
         <v>9.9815157116451017E-2</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <f t="shared" si="10"/>
         <v>5.0699300699300696E-2</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="10">
         <v>44578</v>
       </c>
       <c r="B25">
@@ -10301,29 +10263,29 @@
       <c r="E25">
         <v>10</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="10">
         <f t="shared" si="7"/>
         <v>44578</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <f t="shared" si="8"/>
         <v>5.7964184731385489E-2</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <f t="shared" si="9"/>
         <v>0.10166358595194085</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="11">
         <f t="shared" si="10"/>
         <v>5.0699300699300696E-2</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
         <v>44579</v>
       </c>
       <c r="B26">
@@ -10339,29 +10301,29 @@
       <c r="E26">
         <v>10</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="10">
         <f t="shared" si="7"/>
         <v>44579</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="11">
         <f t="shared" si="8"/>
         <v>6.1734213006597552E-2</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="11">
         <f t="shared" si="9"/>
         <v>0.11275415896487985</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="11">
         <f t="shared" si="10"/>
         <v>5.2447552447552448E-2</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" s="10">
         <v>44580</v>
       </c>
       <c r="B27">
@@ -10377,29 +10339,29 @@
       <c r="E27">
         <v>10</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="10">
         <f t="shared" si="7"/>
         <v>44580</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="11">
         <f t="shared" si="8"/>
         <v>6.6918001885014136E-2</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="11">
         <f t="shared" si="9"/>
         <v>0.12199630314232902</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="11">
         <f t="shared" si="10"/>
         <v>5.7692307692307696E-2</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="10">
         <v>44581</v>
       </c>
       <c r="B28">
@@ -10415,29 +10377,29 @@
       <c r="E28">
         <v>10</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="10">
         <f t="shared" si="7"/>
         <v>44581</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="11">
         <f t="shared" si="8"/>
         <v>6.738925541941565E-2</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="11">
         <f t="shared" si="9"/>
         <v>0.12199630314232902</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="11">
         <f t="shared" si="10"/>
         <v>5.8566433566433568E-2</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
         <v>44582</v>
       </c>
       <c r="B29">
@@ -10453,29 +10415,29 @@
       <c r="E29">
         <v>10</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="10">
         <f t="shared" si="7"/>
         <v>44582</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <f t="shared" si="8"/>
         <v>6.8803016022620164E-2</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <f t="shared" si="9"/>
         <v>0.12384473197781885</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <f t="shared" si="10"/>
         <v>6.0314685314685312E-2</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="11">
         <f t="shared" si="11"/>
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
         <v>44583</v>
       </c>
       <c r="B30">
@@ -10491,29 +10453,29 @@
       <c r="E30">
         <v>11</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="10">
         <f t="shared" si="7"/>
         <v>44583</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="11">
         <f t="shared" ref="H30:H34" si="12">B30/$O$1</f>
         <v>7.163053722902922E-2</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="11">
         <f t="shared" ref="I30:I34" si="13">C30/$O$2</f>
         <v>0.1256931608133087</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <f t="shared" ref="J30:J34" si="14">D30/$O$3</f>
         <v>6.3811188811188815E-2</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="11">
         <f t="shared" si="11"/>
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
         <v>44584</v>
       </c>
       <c r="B31">
@@ -10529,29 +10491,29 @@
       <c r="E31">
         <v>11</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="10">
         <f t="shared" si="7"/>
         <v>44584</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="11">
         <f t="shared" si="12"/>
         <v>7.3044297832233748E-2</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="11">
         <f t="shared" si="13"/>
         <v>0.12939001848428835</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="11">
         <f t="shared" si="14"/>
         <v>6.4685314685314688E-2</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="11">
         <f t="shared" si="11"/>
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
         <v>44585</v>
       </c>
       <c r="B32">
@@ -10567,29 +10529,29 @@
       <c r="E32">
         <v>11</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="10">
         <f t="shared" si="7"/>
         <v>44585</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="11">
         <f t="shared" si="12"/>
         <v>7.3986804901036762E-2</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="11">
         <f t="shared" si="13"/>
         <v>0.13308687615526801</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="11">
         <f t="shared" si="14"/>
         <v>6.4685314685314688E-2</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="11">
         <f t="shared" si="11"/>
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
         <v>44586</v>
       </c>
       <c r="B33">
@@ -10605,29 +10567,29 @@
       <c r="E33">
         <v>11</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="10">
         <f t="shared" si="7"/>
         <v>44586</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <f t="shared" si="12"/>
         <v>7.4458058435438262E-2</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="11">
         <f t="shared" si="13"/>
         <v>0.13308687615526801</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="11">
         <f t="shared" si="14"/>
         <v>6.555944055944056E-2</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="11">
         <f t="shared" si="11"/>
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
         <v>44649</v>
       </c>
       <c r="B34">
@@ -10643,29 +10605,29 @@
       <c r="E34">
         <v>13</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="10">
         <f>A34</f>
         <v>44649</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="11">
         <f t="shared" si="12"/>
         <v>8.1055607917059375E-2</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="11">
         <f t="shared" si="13"/>
         <v>0.14232902033271719</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="11">
         <f t="shared" si="14"/>
         <v>7.167832167832168E-2</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="11">
         <f t="shared" si="11"/>
         <v>2.8384279475982533E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="11"/>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10674,148 +10636,148 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{315F9833-570C-45DC-878A-A024E750C299}">
   <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" style="14"/>
-    <col min="2" max="2" width="16.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="9" style="13"/>
+    <col min="2" max="2" width="16.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
-      <c r="C1" s="14" t="s">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C1" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7">
-      <c r="B2" s="14" t="s">
+      <c r="G1" s="13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7">
-      <c r="B3" s="14" t="s">
+      <c r="G2" s="13" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="14" t="s">
+      <c r="G3" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="14" t="s">
+      <c r="G4" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" s="14" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="14" t="s">
+      <c r="G13" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="14" t="s">
+      <c r="G15" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="14" t="s">
+      <c r="G16" s="13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="14" t="s">
-        <v>279</v>
+      <c r="G17" s="13" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -10824,36 +10786,36 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1016E050-454D-403C-89A4-4628BA77CE62}">
   <dimension ref="C13:I18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="3:9">
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="I13" s="21"/>
-    </row>
-    <row r="14" spans="3:9">
-      <c r="C14" s="21"/>
-      <c r="I14" s="21"/>
-    </row>
-    <row r="15" spans="3:9">
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="3:9">
-      <c r="C16" s="21"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="21"/>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="21"/>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C14" s="16"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LeetCode.xlsx
+++ b/LeetCode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenchen/Projects/Leetcode/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\Leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DEC19C-C1B3-6E4D-A7D6-27516BC12DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C14E94-F861-490D-9CE9-754AFBEB88AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28340" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LeetCode" sheetId="3" r:id="rId1"/>
@@ -23,28 +23,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LC-SQL'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LeetCode!$A$1:$M$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LeetCode!$A$1:$M$161</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="541">
   <si>
     <t>#</t>
   </si>
@@ -233,10 +224,6 @@
   </si>
   <si>
     <t>Merge Intervals</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>先sort，再想象一下O(n) merge方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1165,10 +1152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.geeksforgeeks.org/k-th-element-two-sorted-arrays/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1487,9 +1470,6 @@
     <t>linked list, two pointers</t>
   </si>
   <si>
-    <t>奇数全放左边，偶数全放右边</t>
-  </si>
-  <si>
     <t>two pointer，slow记录最后一个奇数，fast遍历list</t>
   </si>
   <si>
@@ -1500,9 +1480,6 @@
   </si>
   <si>
     <t>list保持顺序进行rotate</t>
-  </si>
-  <si>
-    <t>先生成cycle，再cut</t>
   </si>
   <si>
     <t>Insert into a Sorted Circular Linked List</t>
@@ -1892,13 +1869,64 @@
   </si>
   <si>
     <t>存成stackA和stackB，pop直到有区别的node</t>
+  </si>
+  <si>
+    <t>linked list, hash table</t>
+  </si>
+  <si>
+    <t>先收尾相连生成cycle，再cut</t>
+  </si>
+  <si>
+    <t>奇数位置全放左边，偶数位置全放右边</t>
+  </si>
+  <si>
+    <t>对于2中最小的x，选择y中最小的&gt;x的y对应它。或者反过来：对于 nums2 中最强的敌人，你有两个选择：恰好能赢他 → 用你最小的能赢他的牌去赢，赢不了他 → 用你最没价值的牌（最小值）去送死，保留强牌对付其他人</t>
+  </si>
+  <si>
+    <t>Non-overlapping Intervals</t>
+  </si>
+  <si>
+    <t>greedy</t>
+  </si>
+  <si>
+    <t>按结束时间排序所有区间</t>
+  </si>
+  <si>
+    <t>Number of Distinct Islands</t>
+  </si>
+  <si>
+    <t>平移相似的就是same islands，数有多少个distinct的</t>
+  </si>
+  <si>
+    <t>先DFS找出来所有islands，然后按相对坐标判断每个islands形状。</t>
+  </si>
+  <si>
+    <t>先sort，再想象一下O(n) merge方法</t>
+  </si>
+  <si>
+    <t>overlap的interval合并成一个</t>
+  </si>
+  <si>
+    <t>Interval Scheduling 问题，最多多少个non-overlapping interval</t>
+  </si>
+  <si>
+    <t>Largest Rectangle in Histogram</t>
+  </si>
+  <si>
+    <t>连续柱状图，求最大一个矩形面积</t>
+  </si>
+  <si>
+    <t>用monotonic stack。对每根柱子，最大矩形的高度 = 该柱子高度，宽度 = 向左右两侧能延伸多远（直到遇到比它矮的柱子为止）。</t>
+  </si>
+  <si>
+    <t>Maximal Rectangle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1994,7 +2022,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2036,6 +2064,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2165,7 +2196,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2414,7 +2445,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2663,7 +2694,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -2912,7 +2943,7 @@
             <c:numRef>
               <c:f>progress!$A$2:$A$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3150,7 +3181,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3435,7 +3466,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3684,7 +3715,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -3933,7 +3964,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -4182,7 +4213,7 @@
             <c:numRef>
               <c:f>progress!$G$2:$G$34</c:f>
               <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
+                <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>44197</c:v>
@@ -4420,7 +4451,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6046,22 +6077,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B7B66D-011E-4D1B-AC2F-2C5C53A1B819}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:M157"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M161"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.5" style="9" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="9" customWidth="1"/>
     <col min="3" max="3" width="8.33203125" style="9" customWidth="1"/>
-    <col min="4" max="5" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="9" customWidth="1"/>
     <col min="7" max="7" width="30.33203125" style="9" customWidth="1"/>
-    <col min="8" max="11" width="33.5" style="9" customWidth="1"/>
+    <col min="8" max="11" width="33.44140625" style="9" customWidth="1"/>
     <col min="12" max="13" width="9" style="9"/>
     <col min="14" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="5" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6069,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>2</v>
@@ -6081,10 +6111,10 @@
         <v>8</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
@@ -6092,7 +6122,7 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -6103,354 +6133,360 @@
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="28.8">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:13" ht="43.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.8">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:13" ht="28.8">
       <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="7">
         <v>7</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="7">
         <v>9</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="7">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:13" ht="28.8">
       <c r="A10" s="7">
         <v>19</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="9">
         <v>1</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="7">
         <v>20</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:13" ht="28.8">
       <c r="A12" s="7">
         <v>21</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="9">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:13" ht="28.8">
       <c r="A13" s="7">
         <v>23</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="F13" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:13" ht="28.8">
       <c r="A14" s="7">
         <v>27</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G14" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:13" ht="43.2">
       <c r="A15" s="7">
         <v>33</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F15" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:13" ht="28.8">
       <c r="A16" s="7">
         <v>34</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:8" ht="43.2">
       <c r="A17" s="7">
         <v>36</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="72">
       <c r="A18" s="7">
         <v>42</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>137</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="7">
         <v>49</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="7">
         <v>50</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="H20" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="7">
         <v>53</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="7">
         <v>55</v>
       </c>
@@ -6458,2293 +6494,2408 @@
         <v>56</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+    <row r="23" spans="1:8">
+      <c r="A23" s="15">
         <v>56</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>535</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8">
       <c r="A24" s="7">
         <v>61</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>396</v>
+        <v>393</v>
+      </c>
+      <c r="C24" s="9">
+        <v>1</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="7">
         <v>69</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:8" ht="57.6">
       <c r="A26" s="7">
         <v>74</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>212</v>
-      </c>
       <c r="F26" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="H26" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:8" ht="28.8">
       <c r="A27" s="7">
         <v>83</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="9">
         <v>1</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="64" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
         <v>94</v>
       </c>
+    </row>
+    <row r="28" spans="1:8" ht="72">
+      <c r="A28" s="15">
+        <v>84</v>
+      </c>
       <c r="B28" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="15">
+        <v>85</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="57.6">
+      <c r="A30" s="7">
+        <v>94</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G30" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="H30" s="9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="43.2">
+      <c r="A31" s="7">
+        <v>98</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="7">
+        <v>102</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="7">
+        <v>121</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.8">
+      <c r="A34" s="7">
+        <v>133</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
-        <v>98</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="F34" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="7">
+        <v>136</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.8">
+      <c r="A36" s="7">
+        <v>138</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="9">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="57.6">
+      <c r="A37" s="15">
+        <v>141</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="9">
+        <v>1</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="57.6">
+      <c r="A38" s="15">
+        <v>142</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C38" s="9">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="43.2">
+      <c r="A39" s="7">
+        <v>146</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="7">
         <v>150</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="B40" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="7">
         <v>151</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="B41" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="15">
         <v>152</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7">
-        <v>102</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F30" s="9" t="s">
+      <c r="B42" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="43.2">
+      <c r="A43" s="7">
         <v>155</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7">
+      <c r="B43" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="7">
-        <v>133</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="7">
-        <v>136</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A34" s="7">
-        <v>138</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="64" x14ac:dyDescent="0.2">
-      <c r="A35" s="7">
-        <v>141</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="64" x14ac:dyDescent="0.2">
-      <c r="A36" s="7">
-        <v>142</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="G43" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.8">
+      <c r="A44" s="7">
+        <v>160</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C44" s="9">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H44" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
-        <v>146</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="7">
-        <v>150</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="7">
-        <v>151</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F39" s="9" t="s">
+      <c r="I44" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="7">
+        <v>175</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="15">
-        <v>152</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="7">
-        <v>155</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A42" s="7">
-        <v>160</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="9">
-        <v>1</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="7">
-        <v>175</v>
-      </c>
-      <c r="B43" s="9" t="s">
+      <c r="H45" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="7">
+    </row>
+    <row r="46" spans="1:9" ht="28.8">
+      <c r="A46" s="15">
         <v>198</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="7">
-        <v>200</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="7">
-        <v>202</v>
-      </c>
       <c r="B46" s="9" t="s">
-        <v>366</v>
+        <v>446</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="28.8">
       <c r="A47" s="7">
+        <v>200</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.8">
+      <c r="A48" s="7">
+        <v>202</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28.8">
+      <c r="A49" s="7">
         <v>203</v>
       </c>
-      <c r="B47" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C47" s="9">
-        <v>1</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7">
-        <v>205</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="7">
-        <v>206</v>
-      </c>
       <c r="B49" s="9" t="s">
-        <v>115</v>
+        <v>243</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="7">
+        <v>205</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="7">
+        <v>206</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="9">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="7">
         <v>217</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="7">
+      <c r="B52" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="7">
         <v>219</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="7">
+      <c r="B53" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="28.8">
+      <c r="A54" s="7">
         <v>221</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G52" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="7">
-        <v>224</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="7">
-        <v>225</v>
-      </c>
       <c r="B54" s="9" t="s">
-        <v>358</v>
+        <v>460</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>359</v>
+        <v>309</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>461</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="7">
+        <v>224</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="28.8">
+      <c r="A56" s="7">
+        <v>225</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="28.8">
+      <c r="A57" s="7">
         <v>227</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B57" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="7">
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="7">
         <v>231</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B58" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F58" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="7">
+      <c r="G58" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="72">
+      <c r="A59" s="7">
         <v>232</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B59" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="F59" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="G59" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="32" x14ac:dyDescent="0.2">
-      <c r="A58" s="7">
+    </row>
+    <row r="60" spans="1:9" ht="28.8">
+      <c r="A60" s="7">
         <v>234</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" s="9">
-        <v>1</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="7">
-        <v>236</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="48" x14ac:dyDescent="0.2">
-      <c r="A60" s="7">
-        <v>237</v>
-      </c>
       <c r="B60" s="9" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="C60" s="9">
         <v>1</v>
       </c>
       <c r="D60" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="72">
+      <c r="A61" s="7">
+        <v>236</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="43.2">
+      <c r="A62" s="7">
+        <v>237</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" s="9">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="G62" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H62" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="G60" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="H60" s="9" t="s">
+    </row>
+    <row r="63" spans="1:9" ht="28.8">
+      <c r="A63" s="7">
+        <v>239</v>
+      </c>
+      <c r="B63" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="7">
-        <v>239</v>
-      </c>
-      <c r="B61" s="9" t="s">
+      <c r="D63" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="F63" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="H61" s="9" t="s">
+      <c r="I63" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="43.2">
+      <c r="A64" s="7">
+        <v>240</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="28.8">
+      <c r="A65" s="7">
+        <v>249</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="7">
+        <v>278</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="57.6">
+      <c r="A67" s="7">
+        <v>279</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="72">
+      <c r="A68" s="7">
+        <v>286</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="57.6">
+      <c r="A69" s="7">
+        <v>287</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="K69" s="8"/>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70" s="7">
+        <v>288</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="K70" s="8"/>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="7">
+        <v>290</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="K71" s="8"/>
+    </row>
+    <row r="72" spans="1:11" ht="28.8">
+      <c r="A72" s="7">
+        <v>297</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="K72" s="8"/>
+    </row>
+    <row r="73" spans="1:11" ht="28.8">
+      <c r="A73" s="7">
+        <v>300</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K73" s="8"/>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="15">
+        <v>322</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="H74" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I61" s="12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="7">
-        <v>240</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="7">
-        <v>249</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="7">
-        <v>278</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="7">
-        <v>279</v>
-      </c>
-      <c r="B65" s="9" t="s">
+      <c r="K74" s="8"/>
+    </row>
+    <row r="75" spans="1:11" ht="28.8">
+      <c r="A75" s="7">
+        <v>323</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="K75" s="8"/>
+    </row>
+    <row r="76" spans="1:11" ht="43.2">
+      <c r="A76" s="7">
+        <v>328</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C76" s="9">
+        <v>1</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K76" s="8"/>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="7">
+        <v>332</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="K77" s="8"/>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="7">
+        <v>346</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="K78" s="8"/>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="7">
+        <v>347</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="K79" s="8"/>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="7">
+        <v>349</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="9">
+        <v>1</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="7">
         <v>350</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="64" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="7">
-        <v>286</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="64" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7">
-        <v>287</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="J67" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="K67" s="8"/>
-    </row>
-    <row r="68" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="7">
-        <v>288</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="K68" s="8"/>
-    </row>
-    <row r="69" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="7">
-        <v>290</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="K69" s="8"/>
-    </row>
-    <row r="70" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="7">
-        <v>297</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="K70" s="8"/>
-    </row>
-    <row r="71" spans="1:11" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="7">
-        <v>300</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="K71" s="8"/>
-    </row>
-    <row r="72" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="7">
-        <v>322</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="K72" s="8"/>
-    </row>
-    <row r="73" spans="1:11" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="7">
-        <v>323</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="K73" s="8"/>
-    </row>
-    <row r="74" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A74" s="7">
-        <v>328</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F74" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="K74" s="8"/>
-    </row>
-    <row r="75" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="7">
-        <v>332</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="K75" s="8"/>
-    </row>
-    <row r="76" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="7">
-        <v>346</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K76" s="8"/>
-    </row>
-    <row r="77" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="7">
-        <v>347</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K77" s="8"/>
-    </row>
-    <row r="78" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
-        <v>349</v>
-      </c>
-      <c r="B78" s="9" t="s">
+      <c r="B81" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" s="9">
+        <v>1</v>
+      </c>
+      <c r="D81" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D78" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="7">
-        <v>350</v>
-      </c>
-      <c r="B79" s="9" t="s">
+      <c r="F81" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D79" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="7">
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="7">
         <v>359</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="7">
+      <c r="B82" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="7">
         <v>374</v>
       </c>
-      <c r="B81" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="7">
+      <c r="B83" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="28.8">
+      <c r="A84" s="7">
         <v>380</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="15">
-        <v>384</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="7">
-        <v>387</v>
-      </c>
       <c r="B84" s="9" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="7">
+        <v>437</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="15">
+        <v>384</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="7">
+        <v>387</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="7">
         <v>394</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B87" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D87" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="7">
+      <c r="F87" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="43.2">
+      <c r="A88" s="7">
         <v>417</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B88" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F88" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D86" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F86" s="9" t="s">
+      <c r="G88" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="28.8">
+      <c r="A89" s="7">
+        <v>430</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C89" s="9">
+        <v>1</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="43.2">
+      <c r="A90" s="15">
+        <v>435</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C90" s="9">
+        <v>1</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="28.8">
+      <c r="A91" s="7">
+        <v>445</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="9">
+        <v>1</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A87" s="7">
-        <v>430</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A88" s="7">
-        <v>445</v>
-      </c>
-      <c r="B88" s="9" t="s">
+      <c r="F91" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D88" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="7">
+      <c r="H91" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="7">
         <v>450</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B92" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="D89" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="7">
+    </row>
+    <row r="93" spans="1:8" ht="28.8">
+      <c r="A93" s="7">
         <v>454</v>
       </c>
-      <c r="B90" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="15">
-        <v>470</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="7">
-        <v>494</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="7">
-        <v>520</v>
-      </c>
       <c r="B93" s="9" t="s">
-        <v>493</v>
+        <v>432</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="7">
+      <c r="F93" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="15">
+        <v>470</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="28.8">
+      <c r="A95" s="7">
+        <v>494</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="7">
+        <v>520</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="28.8">
+      <c r="A97" s="7">
         <v>542</v>
       </c>
-      <c r="B94" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="7">
+      <c r="B97" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="7">
         <v>547</v>
       </c>
-      <c r="B95" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="7">
-        <v>554</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="7">
-        <v>572</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="7">
-        <v>599</v>
-      </c>
       <c r="B98" s="9" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" s="7">
+        <v>554</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="43.2">
+      <c r="A100" s="7">
+        <v>572</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="7">
+        <v>599</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="7">
         <v>605</v>
       </c>
-      <c r="B99" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="D99" s="8" t="s">
+      <c r="B102" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="7">
+        <v>617</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="72">
+      <c r="A104" s="7">
+        <v>622</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C104" s="9">
+        <v>1</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="7">
-        <v>617</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="64" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="7">
-        <v>622</v>
-      </c>
-      <c r="B101" s="9" t="s">
+      <c r="F104" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="H104" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="D101" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="7">
+    </row>
+    <row r="105" spans="1:10" ht="28.8">
+      <c r="A105" s="7">
         <v>652</v>
       </c>
-      <c r="B102" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="7">
+      <c r="B105" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="28.8">
+      <c r="A106" s="15">
+        <v>694</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="7">
         <v>704</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D103" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="H103" s="9" t="s">
+      <c r="B107" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F107" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A104" s="7">
+      <c r="G107" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="43.2">
+      <c r="A108" s="7">
         <v>706</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B108" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" s="9">
+        <v>1</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F108" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="G108" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="H108" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="I108" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="J108" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="H104" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="J104" s="9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="7">
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="7">
         <v>707</v>
       </c>
-      <c r="B105" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="D105" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A106" s="7">
+      <c r="B109" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C109" s="9">
+        <v>1</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="28.8">
+      <c r="A110" s="7">
         <v>708</v>
       </c>
-      <c r="B106" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="7">
-        <v>733</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="7">
-        <v>739</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="7">
-        <v>740</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="7">
-        <v>746</v>
-      </c>
       <c r="B110" s="9" t="s">
-        <v>452</v>
+        <v>395</v>
+      </c>
+      <c r="C110" s="9">
+        <v>1</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111" s="7">
+        <v>733</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="57.6">
+      <c r="A112" s="7">
+        <v>739</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="28.8">
+      <c r="A113" s="7">
+        <v>740</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="7">
+        <v>746</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="43.2">
+      <c r="A115" s="7">
         <v>752</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B115" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="D111" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F111" s="9" t="s">
+      <c r="H115" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="G111" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="7">
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="7">
         <v>797</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="7">
+      <c r="B116" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="7">
         <v>841</v>
       </c>
-      <c r="B113" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="7">
-        <v>849</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="G114" s="9" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="7">
-        <v>870</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="7">
-        <v>875</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="7">
-        <v>905</v>
-      </c>
       <c r="B117" s="9" t="s">
-        <v>516</v>
+        <v>354</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="F117" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="28.8">
       <c r="A118" s="7">
-        <v>922</v>
+        <v>849</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>517</v>
+        <v>404</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G118" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="129.6">
       <c r="A119" s="7">
-        <v>923</v>
+        <v>870</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+      <c r="C119" s="9">
+        <v>1</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" s="7">
-        <v>941</v>
+        <v>875</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9">
       <c r="A121" s="7">
+        <v>905</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="7">
+        <v>922</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="28.8">
+      <c r="A123" s="7">
+        <v>923</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="7">
+        <v>941</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="28.8">
+      <c r="A125" s="7">
         <v>973</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B125" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F125" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="D121" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H121" s="9" t="s">
+      <c r="H125" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="I125" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="I121" s="9" t="s">
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="7">
+        <v>1137</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="72">
+      <c r="A127" s="7">
+        <v>1143</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="28.8">
+      <c r="A128" s="7">
+        <v>1198</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="28.8">
+      <c r="A129" s="7">
+        <v>1209</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="28.8">
+      <c r="A130" s="7">
+        <v>1249</v>
+      </c>
+      <c r="B130" s="9" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="7">
-        <v>1137</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G122" s="9" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="80" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="7">
-        <v>1143</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="D123" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="7">
-        <v>1198</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="7">
-        <v>1209</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D125" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G125" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="7">
-        <v>1249</v>
-      </c>
-      <c r="B126" s="9" t="s">
+      <c r="D130" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="F130" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="F126" s="9" t="s">
+      <c r="H130" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H126" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="7">
+    </row>
+    <row r="131" spans="1:10" ht="28.8">
+      <c r="A131" s="7">
         <v>1291</v>
       </c>
-      <c r="B127" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="G127" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="7">
-        <v>1305</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="7">
-        <v>1329</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="G129" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="15">
-        <v>1387</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="D130" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="7">
-        <v>1572</v>
-      </c>
       <c r="B131" s="9" t="s">
-        <v>347</v>
+        <v>484</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="15">
-        <v>1770</v>
+      <c r="G131" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="28.8">
+      <c r="A132" s="7">
+        <v>1305</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>463</v>
+        <v>499</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="43.2">
       <c r="A133" s="7">
-        <v>1971</v>
+        <v>1329</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>468</v>
+        <v>336</v>
       </c>
       <c r="D133" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="F133" s="9" t="s">
-        <v>355</v>
+      <c r="E133" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="7">
-        <v>2119</v>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="15">
+        <v>1387</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D134" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="E134" s="8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
       <c r="A135" s="7">
-        <v>2129</v>
+        <v>1572</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>491</v>
+        <v>345</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="7">
-        <v>2133</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="28.8">
+      <c r="A136" s="15">
+        <v>1770</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>345</v>
+        <v>459</v>
       </c>
       <c r="D136" s="8" t="s">
         <v>307</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G136" s="9" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="28.8">
       <c r="A137" s="7">
+        <v>1971</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="7">
+        <v>2119</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="7">
+        <v>2129</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="43.2">
+      <c r="A140" s="7">
+        <v>2133</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="7">
         <v>2138</v>
       </c>
-      <c r="B137" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="D137" s="8" t="s">
+      <c r="B141" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="28.8">
+      <c r="A142" s="7">
+        <v>2139</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="D142" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="7">
-        <v>2139</v>
-      </c>
-      <c r="B138" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="D138" s="8" t="s">
+    <row r="143" spans="1:10" ht="28.8">
+      <c r="A143" s="7">
+        <v>2140</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F143" s="9" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" ht="48" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="7">
-        <v>2140</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="G139" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="112" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="7">
+      <c r="G143" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="115.2">
+      <c r="A144" s="7">
         <v>2141</v>
       </c>
-      <c r="B140" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="H140" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="I140" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="J140" s="12" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="7">
+      <c r="B144" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="H144" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="28.8">
+      <c r="A145" s="7">
         <v>2148</v>
       </c>
-      <c r="B141" s="9" t="s">
+      <c r="B145" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="7">
+        <v>2149</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="28.8">
+      <c r="A147" s="7">
+        <v>2150</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="28.8">
+      <c r="A148" s="7">
+        <v>2151</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="H148" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="D141" s="8" t="s">
+    </row>
+    <row r="149" spans="1:9" ht="28.8">
+      <c r="A149" s="7">
+        <v>2154</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="28.8">
+      <c r="A150" s="7">
+        <v>2155</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D150" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="7">
-        <v>2149</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="7">
-        <v>2150</v>
-      </c>
-      <c r="B143" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="D143" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="7">
-        <v>2151</v>
-      </c>
-      <c r="B144" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="D144" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="G144" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="H144" s="9" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="7">
-        <v>2154</v>
-      </c>
-      <c r="B145" s="9" t="s">
+    <row r="151" spans="1:9" ht="28.8">
+      <c r="A151" s="7">
+        <v>2156</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="28.8">
+      <c r="A152" s="7">
+        <v>2164</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="28.8">
+      <c r="A153" s="7">
+        <v>2165</v>
+      </c>
+      <c r="B153" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="D145" s="8" t="s">
+      <c r="D153" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="7">
-        <v>2155</v>
-      </c>
-      <c r="B146" s="9" t="s">
+      <c r="I153" s="12"/>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="7">
+        <v>2166</v>
+      </c>
+      <c r="B154" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="D146" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="7">
-        <v>2156</v>
-      </c>
-      <c r="B147" s="9" t="s">
+      <c r="D154" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="I154" s="12"/>
+    </row>
+    <row r="155" spans="1:9" ht="129.6">
+      <c r="A155" s="7">
+        <v>2167</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="I155" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="D147" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="7">
-        <v>2164</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="D148" s="8" t="s">
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="7">
+        <v>2169</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="28.8">
+      <c r="A157" s="7">
+        <v>2170</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D157" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="7">
-        <v>2165</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="I149" s="12"/>
-    </row>
-    <row r="150" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="7">
-        <v>2166</v>
-      </c>
-      <c r="B150" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="D150" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="I150" s="12"/>
-    </row>
-    <row r="151" spans="1:9" ht="128" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="7">
-        <v>2167</v>
-      </c>
-      <c r="B151" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D151" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="H151" s="9" t="s">
+    <row r="158" spans="1:9" ht="28.8">
+      <c r="A158" s="7">
+        <v>2171</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="7">
+        <v>2194</v>
+      </c>
+      <c r="B159" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="I151" s="12" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="7">
-        <v>2169</v>
-      </c>
-      <c r="B152" s="9" t="s">
+      <c r="D159" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="28.8">
+      <c r="A160" s="7">
+        <v>2195</v>
+      </c>
+      <c r="B160" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="D160" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="7">
-        <v>2170</v>
-      </c>
-      <c r="B153" s="9" t="s">
+    <row r="161" spans="1:4" ht="28.8">
+      <c r="A161" s="7">
+        <v>2196</v>
+      </c>
+      <c r="B161" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="D153" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" ht="32" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="7">
-        <v>2171</v>
-      </c>
-      <c r="B154" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="7">
-        <v>2194</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="D155" s="8" t="s">
+      <c r="D161" s="8" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="7">
-        <v>2195</v>
-      </c>
-      <c r="B156" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="D156" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="7">
-        <v>2196</v>
-      </c>
-      <c r="B157" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M157" xr:uid="{1C56C913-064E-423F-843C-70445A14D676}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="linked list"/>
-        <filter val="linked list, array, hash table"/>
-        <filter val="linked list, dfs"/>
-        <filter val="linked list, hash table"/>
-        <filter val="linked list, hash table, two pointers"/>
-        <filter val="linked list, heap, divide and conquer"/>
-        <filter val="linked list, stack"/>
-        <filter val="linked list, two pointers"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M161" xr:uid="{1C56C913-064E-423F-843C-70445A14D676}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I61" r:id="rId1" xr:uid="{1A0B9458-2E5B-46D8-B44E-F8E45F0E8738}"/>
+    <hyperlink ref="I63" r:id="rId1" xr:uid="{1A0B9458-2E5B-46D8-B44E-F8E45F0E8738}"/>
     <hyperlink ref="G6" r:id="rId2" xr:uid="{EA113FAB-F94F-4508-8ED6-94388E6A09A7}"/>
-    <hyperlink ref="J140" r:id="rId3" xr:uid="{A363DD3B-75EA-422A-B19E-76CA6A2E19E8}"/>
-    <hyperlink ref="I151" r:id="rId4" xr:uid="{F9F4DB09-A6FA-4D22-B87C-A70C4E2A9F74}"/>
+    <hyperlink ref="J144" r:id="rId3" xr:uid="{A363DD3B-75EA-422A-B19E-76CA6A2E19E8}"/>
+    <hyperlink ref="I155" r:id="rId4" xr:uid="{F9F4DB09-A6FA-4D22-B87C-A70C4E2A9F74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
@@ -8754,17 +8905,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA4FB45-65C7-4804-B2C5-A3763C8E324A}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5" customWidth="1"/>
-    <col min="3" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" customWidth="1"/>
-    <col min="7" max="7" width="31.1640625" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
+    <col min="7" max="7" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="5" customFormat="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8781,46 +8932,46 @@
         <v>8</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="8" customFormat="1" ht="28.8">
       <c r="A2" s="7">
         <v>511</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="8" customFormat="1" ht="28.8">
       <c r="A3" s="7">
         <v>512</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -8832,18 +8983,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8863,7 +9014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8880,7 +9031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3">
         <v>83</v>
       </c>
@@ -8900,7 +9051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4">
         <v>322</v>
       </c>
@@ -8923,7 +9074,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5">
         <v>443</v>
       </c>
@@ -8943,7 +9094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6">
         <v>532</v>
       </c>
@@ -8966,7 +9117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7">
         <v>547</v>
       </c>
@@ -8980,7 +9131,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -8989,7 +9140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8">
         <v>647</v>
       </c>
@@ -9003,7 +9154,7 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F8" t="s">
         <v>40</v>
@@ -9012,7 +9163,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9">
         <v>724</v>
       </c>
@@ -9032,7 +9183,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10">
         <v>733</v>
       </c>
@@ -9050,7 +9201,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11">
         <v>780</v>
       </c>
@@ -9070,7 +9221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12">
         <v>1041</v>
       </c>
@@ -9093,7 +9244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13">
         <v>1051</v>
       </c>
@@ -9113,7 +9264,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14">
         <v>1163</v>
       </c>
@@ -9145,12 +9296,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8661F369-1314-4056-8910-E5294C54F722}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="5" customFormat="1" ht="28.8">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -9167,10 +9318,10 @@
         <v>8</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -9178,15 +9329,15 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" s="8" customFormat="1">
       <c r="A2" s="8">
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -9196,15 +9347,15 @@
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
     </row>
-    <row r="3" spans="1:12" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" s="8" customFormat="1">
       <c r="A3" s="8">
         <v>29</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -9214,29 +9365,29 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="8">
         <v>56</v>
       </c>
@@ -9244,51 +9395,51 @@
         <v>58</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="8">
         <v>146</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>564</v>
       </c>
       <c r="B9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>1779</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -9299,62 +9450,62 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7C2A69-420F-4346-8F8A-01973B865F7F}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.109375" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G1" s="10" t="str">
         <f>A1</f>
         <v>Date</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O1">
         <v>2122</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15">
       <c r="A2" s="10">
         <v>44197</v>
       </c>
@@ -9398,7 +9549,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15">
       <c r="A3" s="10">
         <v>44258</v>
       </c>
@@ -9436,13 +9587,13 @@
         <v>8.7336244541484712E-3</v>
       </c>
       <c r="N3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O3">
         <v>1144</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15">
       <c r="A4" s="10">
         <v>44259</v>
       </c>
@@ -9480,13 +9631,13 @@
         <v>8.7336244541484712E-3</v>
       </c>
       <c r="N4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15">
       <c r="A5" s="10">
         <v>44260</v>
       </c>
@@ -9524,7 +9675,7 @@
         <v>8.7336244541484712E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15">
       <c r="A6" s="10">
         <v>44263</v>
       </c>
@@ -9562,7 +9713,7 @@
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15">
       <c r="A7" s="10">
         <v>44264</v>
       </c>
@@ -9600,7 +9751,7 @@
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15">
       <c r="A8" s="10">
         <v>44266</v>
       </c>
@@ -9638,7 +9789,7 @@
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15">
       <c r="A9" s="10">
         <v>44270</v>
       </c>
@@ -9676,7 +9827,7 @@
         <v>1.3100436681222707E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15">
       <c r="A10" s="10">
         <v>44273</v>
       </c>
@@ -9714,7 +9865,7 @@
         <v>1.5283842794759825E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15">
       <c r="A11" s="10">
         <v>44274</v>
       </c>
@@ -9752,7 +9903,7 @@
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15">
       <c r="A12" s="10">
         <v>44277</v>
       </c>
@@ -9790,7 +9941,7 @@
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15">
       <c r="A13" s="10">
         <v>44278</v>
       </c>
@@ -9828,7 +9979,7 @@
         <v>1.7467248908296942E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15">
       <c r="A14" s="10">
         <v>44280</v>
       </c>
@@ -9866,7 +10017,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15">
       <c r="A15" s="10">
         <v>44292</v>
       </c>
@@ -9904,7 +10055,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15">
       <c r="A16" s="10">
         <v>44364</v>
       </c>
@@ -9942,7 +10093,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17" s="10">
         <v>44369</v>
       </c>
@@ -9980,7 +10131,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="10">
         <v>44558</v>
       </c>
@@ -10018,7 +10169,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" s="10">
         <v>44571</v>
       </c>
@@ -10056,7 +10207,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="10">
         <v>44572</v>
       </c>
@@ -10094,7 +10245,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="10">
         <v>44573</v>
       </c>
@@ -10132,7 +10283,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22" s="10">
         <v>44574</v>
       </c>
@@ -10170,7 +10321,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" s="10">
         <v>44576</v>
       </c>
@@ -10208,7 +10359,7 @@
         <v>1.9650655021834062E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" s="10">
         <v>44577</v>
       </c>
@@ -10246,7 +10397,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" s="10">
         <v>44578</v>
       </c>
@@ -10284,7 +10435,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26" s="10">
         <v>44579</v>
       </c>
@@ -10322,7 +10473,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27" s="10">
         <v>44580</v>
       </c>
@@ -10360,7 +10511,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" s="10">
         <v>44581</v>
       </c>
@@ -10398,7 +10549,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29" s="10">
         <v>44582</v>
       </c>
@@ -10436,7 +10587,7 @@
         <v>2.1834061135371178E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" s="10">
         <v>44583</v>
       </c>
@@ -10474,7 +10625,7 @@
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31" s="10">
         <v>44584</v>
       </c>
@@ -10512,7 +10663,7 @@
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" s="10">
         <v>44585</v>
       </c>
@@ -10550,7 +10701,7 @@
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" s="10">
         <v>44586</v>
       </c>
@@ -10588,7 +10739,7 @@
         <v>2.4017467248908297E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34" s="10">
         <v>44649</v>
       </c>
@@ -10626,7 +10777,7 @@
         <v>2.8384279475982533E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" s="10"/>
     </row>
   </sheetData>
@@ -10639,145 +10790,145 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{315F9833-570C-45DC-878A-A024E750C299}">
   <dimension ref="B1:G17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="13"/>
-    <col min="2" max="2" width="16.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:7">
       <c r="C1" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>255</v>
-      </c>
       <c r="G1" s="13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7">
       <c r="B2" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="G4" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="13" t="s">
+      <c r="G13" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="13" t="s">
+      <c r="G15" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="13" t="s">
-        <v>204</v>
-      </c>
       <c r="G16" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -10789,32 +10940,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1016E050-454D-403C-89A4-4628BA77CE62}">
   <dimension ref="C13:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:9">
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="I13" s="16"/>
     </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:9">
       <c r="C14" s="16"/>
       <c r="I14" s="16"/>
     </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:9">
       <c r="C15" s="16"/>
     </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:9">
       <c r="C16" s="16"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:3">
       <c r="C17" s="16"/>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:3">
       <c r="C18" s="16"/>
     </row>
   </sheetData>

--- a/LeetCode.xlsx
+++ b/LeetCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\Leetcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C14E94-F861-490D-9CE9-754AFBEB88AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D3D984-85B0-4720-8561-00FC4537480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
